--- a/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rade6a59cdf3c4154"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Rb1e8ccd137a64f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R7c3fba741788499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R43379f981a264760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R757e56d2300a42f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R86b55d21c0164c2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+  </x:numFmts>
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -39,6 +42,11 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -53,7 +61,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -181,11 +189,39 @@
         <x:color rgb="FFB4C6E7"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB4C6E7"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="double">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB4C6E7"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="double">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB4C6E7"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -266,6 +302,42 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -487,7 +559,7 @@
     <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="60" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -607,7 +679,7 @@
       <x:c r="R2" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S2" s="9" t="n">
+      <x:c r="S2" s="9" t="str">
         <x:v>3731005</x:v>
       </x:c>
       <x:c r="T2" s="10" t="str">
@@ -668,7 +740,7 @@
       <x:c r="R3" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S3" s="9" t="n">
+      <x:c r="S3" s="9" t="str">
         <x:v>3731096</x:v>
       </x:c>
       <x:c r="T3" s="10" t="str">
@@ -729,7 +801,7 @@
       <x:c r="R4" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S4" s="9" t="n">
+      <x:c r="S4" s="9" t="str">
         <x:v>3741046</x:v>
       </x:c>
       <x:c r="T4" s="10" t="str">
@@ -790,7 +862,7 @@
       <x:c r="R5" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S5" s="9" t="n">
+      <x:c r="S5" s="9" t="str">
         <x:v>3741686</x:v>
       </x:c>
       <x:c r="T5" s="10" t="str">
@@ -851,7 +923,7 @@
       <x:c r="R6" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S6" s="9" t="n">
+      <x:c r="S6" s="9" t="str">
         <x:v>3741696</x:v>
       </x:c>
       <x:c r="T6" s="10" t="str">
@@ -912,7 +984,7 @@
       <x:c r="R7" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S7" s="9" t="n">
+      <x:c r="S7" s="9" t="str">
         <x:v>4330100</x:v>
       </x:c>
       <x:c r="T7" s="10" t="str">
@@ -973,7 +1045,7 @@
       <x:c r="R8" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S8" s="9" t="n">
+      <x:c r="S8" s="9" t="str">
         <x:v>4330242</x:v>
       </x:c>
       <x:c r="T8" s="10" t="str">
@@ -1034,7 +1106,7 @@
       <x:c r="R9" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S9" s="9" t="n">
+      <x:c r="S9" s="9" t="str">
         <x:v>4330297</x:v>
       </x:c>
       <x:c r="T9" s="10" t="str">
@@ -1095,7 +1167,7 @@
       <x:c r="R10" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S10" s="9" t="n">
+      <x:c r="S10" s="9" t="str">
         <x:v>4330377</x:v>
       </x:c>
       <x:c r="T10" s="10" t="str">
@@ -1156,7 +1228,7 @@
       <x:c r="R11" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S11" s="9" t="n">
+      <x:c r="S11" s="9" t="str">
         <x:v>4330378</x:v>
       </x:c>
       <x:c r="T11" s="10" t="str">
@@ -1217,7 +1289,7 @@
       <x:c r="R12" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S12" s="9" t="n">
+      <x:c r="S12" s="9" t="str">
         <x:v>4330382</x:v>
       </x:c>
       <x:c r="T12" s="10" t="str">
@@ -1278,7 +1350,7 @@
       <x:c r="R13" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S13" s="9" t="n">
+      <x:c r="S13" s="9" t="str">
         <x:v>4330427</x:v>
       </x:c>
       <x:c r="T13" s="10" t="str">
@@ -1339,7 +1411,7 @@
       <x:c r="R14" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S14" s="9" t="n">
+      <x:c r="S14" s="9" t="str">
         <x:v>4814709</x:v>
       </x:c>
       <x:c r="T14" s="10" t="str">
@@ -1400,7 +1472,7 @@
       <x:c r="R15" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S15" s="9" t="n">
+      <x:c r="S15" s="9" t="str">
         <x:v>4814712</x:v>
       </x:c>
       <x:c r="T15" s="10" t="str">
@@ -1461,7 +1533,7 @@
       <x:c r="R16" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S16" s="9" t="n">
+      <x:c r="S16" s="9" t="str">
         <x:v>4814714</x:v>
       </x:c>
       <x:c r="T16" s="10" t="str">
@@ -1527,7 +1599,7 @@
       <x:c r="R17" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S17" s="9" t="n">
+      <x:c r="S17" s="9" t="str">
         <x:v>5155209</x:v>
       </x:c>
       <x:c r="T17" s="10" t="str">
@@ -1588,7 +1660,7 @@
       <x:c r="R18" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S18" s="9" t="n">
+      <x:c r="S18" s="9" t="str">
         <x:v>5155246</x:v>
       </x:c>
       <x:c r="T18" s="10" t="str">
@@ -1649,7 +1721,7 @@
       <x:c r="R19" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S19" s="9" t="n">
+      <x:c r="S19" s="9" t="str">
         <x:v>4324654</x:v>
       </x:c>
       <x:c r="T19" s="10" t="str">
@@ -1710,7 +1782,7 @@
       <x:c r="R20" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S20" s="9" t="n">
+      <x:c r="S20" s="9" t="str">
         <x:v>4330151</x:v>
       </x:c>
       <x:c r="T20" s="10" t="str">
@@ -1772,7 +1844,7 @@
       <x:c r="R21" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S21" s="9" t="n">
+      <x:c r="S21" s="9" t="str">
         <x:v>4814710</x:v>
       </x:c>
       <x:c r="T21" s="10" t="str">
@@ -1833,7 +1905,7 @@
       <x:c r="R22" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S22" s="9" t="n">
+      <x:c r="S22" s="9" t="str">
         <x:v>3786173</x:v>
       </x:c>
       <x:c r="T22" s="10" t="str">
@@ -1897,7 +1969,7 @@
       <x:c r="R23" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S23" s="9" t="n">
+      <x:c r="S23" s="9" t="str">
         <x:v>3787763</x:v>
       </x:c>
       <x:c r="T23" s="10" t="str">
@@ -1958,7 +2030,7 @@
       <x:c r="R24" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S24" s="9" t="n">
+      <x:c r="S24" s="9" t="str">
         <x:v>3790469</x:v>
       </x:c>
       <x:c r="T24" s="10" t="str">
@@ -2019,7 +2091,7 @@
       <x:c r="R25" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S25" s="9" t="n">
+      <x:c r="S25" s="9" t="str">
         <x:v>3790521</x:v>
       </x:c>
       <x:c r="T25" s="10" t="str">
@@ -2080,7 +2152,7 @@
       <x:c r="R26" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S26" s="9" t="n">
+      <x:c r="S26" s="9" t="str">
         <x:v>3790723</x:v>
       </x:c>
       <x:c r="T26" s="10" t="str">
@@ -2141,7 +2213,7 @@
       <x:c r="R27" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S27" s="9" t="n">
+      <x:c r="S27" s="9" t="str">
         <x:v>3790887</x:v>
       </x:c>
       <x:c r="T27" s="10" t="str">
@@ -2202,7 +2274,7 @@
       <x:c r="R28" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S28" s="9" t="n">
+      <x:c r="S28" s="9" t="str">
         <x:v>3790932</x:v>
       </x:c>
       <x:c r="T28" s="10" t="str">
@@ -2263,7 +2335,7 @@
       <x:c r="R29" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S29" s="9" t="n">
+      <x:c r="S29" s="9" t="str">
         <x:v>4528768</x:v>
       </x:c>
       <x:c r="T29" s="10" t="str">
@@ -2324,7 +2396,7 @@
       <x:c r="R30" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S30" s="9" t="n">
+      <x:c r="S30" s="9" t="str">
         <x:v>4529083</x:v>
       </x:c>
       <x:c r="T30" s="10" t="str">
@@ -2385,7 +2457,7 @@
       <x:c r="R31" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S31" s="9" t="n">
+      <x:c r="S31" s="9" t="str">
         <x:v>4814263</x:v>
       </x:c>
       <x:c r="T31" s="10" t="str">
@@ -2446,7 +2518,7 @@
       <x:c r="R32" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S32" s="9" t="n">
+      <x:c r="S32" s="9" t="str">
         <x:v>4814281</x:v>
       </x:c>
       <x:c r="T32" s="10" t="str">
@@ -2507,7 +2579,7 @@
       <x:c r="R33" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S33" s="9" t="n">
+      <x:c r="S33" s="9" t="str">
         <x:v>4814284</x:v>
       </x:c>
       <x:c r="T33" s="10" t="str">
@@ -2570,7 +2642,7 @@
       <x:c r="R34" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S34" s="9" t="n">
+      <x:c r="S34" s="9" t="str">
         <x:v>4814331</x:v>
       </x:c>
       <x:c r="T34" s="10" t="str">
@@ -2631,7 +2703,7 @@
       <x:c r="R35" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S35" s="9" t="n">
+      <x:c r="S35" s="9" t="str">
         <x:v>4814343</x:v>
       </x:c>
       <x:c r="T35" s="10" t="str">
@@ -2692,7 +2764,7 @@
       <x:c r="R36" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S36" s="9" t="n">
+      <x:c r="S36" s="9" t="str">
         <x:v>4814523</x:v>
       </x:c>
       <x:c r="T36" s="10" t="str">
@@ -2753,7 +2825,7 @@
       <x:c r="R37" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S37" s="9" t="n">
+      <x:c r="S37" s="9" t="str">
         <x:v>4814536</x:v>
       </x:c>
       <x:c r="T37" s="10" t="str">
@@ -2814,7 +2886,7 @@
       <x:c r="R38" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S38" s="9" t="n">
+      <x:c r="S38" s="9" t="str">
         <x:v>4814857</x:v>
       </x:c>
       <x:c r="T38" s="10" t="str">
@@ -2875,7 +2947,7 @@
       <x:c r="R39" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S39" s="9" t="n">
+      <x:c r="S39" s="9" t="str">
         <x:v>4814980</x:v>
       </x:c>
       <x:c r="T39" s="10" t="str">
@@ -2936,7 +3008,7 @@
       <x:c r="R40" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S40" s="9" t="n">
+      <x:c r="S40" s="9" t="str">
         <x:v>4814982</x:v>
       </x:c>
       <x:c r="T40" s="10" t="str">
@@ -2997,7 +3069,7 @@
       <x:c r="R41" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S41" s="9" t="n">
+      <x:c r="S41" s="9" t="str">
         <x:v>4814983</x:v>
       </x:c>
       <x:c r="T41" s="10" t="str">
@@ -3058,7 +3130,7 @@
       <x:c r="R42" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S42" s="9" t="n">
+      <x:c r="S42" s="9" t="str">
         <x:v>4814998</x:v>
       </x:c>
       <x:c r="T42" s="10" t="str">
@@ -3119,7 +3191,7 @@
       <x:c r="R43" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S43" s="9" t="n">
+      <x:c r="S43" s="9" t="str">
         <x:v>5098989</x:v>
       </x:c>
       <x:c r="T43" s="10" t="str">
@@ -3180,7 +3252,7 @@
       <x:c r="R44" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S44" s="9" t="n">
+      <x:c r="S44" s="9" t="str">
         <x:v>5098990</x:v>
       </x:c>
       <x:c r="T44" s="10" t="str">
@@ -3241,7 +3313,7 @@
       <x:c r="R45" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S45" s="9" t="n">
+      <x:c r="S45" s="9" t="str">
         <x:v>6900284</x:v>
       </x:c>
       <x:c r="T45" s="10" t="str">
@@ -3296,7 +3368,7 @@
       <x:c r="R46" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S46" s="9" t="n">
+      <x:c r="S46" s="9" t="str">
         <x:v>5098992</x:v>
       </x:c>
       <x:c r="T46" s="10" t="str">
@@ -3360,7 +3432,7 @@
       <x:c r="R47" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S47" s="9" t="n">
+      <x:c r="S47" s="9" t="str">
         <x:v>4330178</x:v>
       </x:c>
       <x:c r="T47" s="10" t="str">
@@ -3424,7 +3496,7 @@
       <x:c r="R48" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S48" s="9" t="n">
+      <x:c r="S48" s="9" t="str">
         <x:v>4330318</x:v>
       </x:c>
       <x:c r="T48" s="10" t="str">
@@ -3489,7 +3561,7 @@
       <x:c r="R49" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S49" s="9" t="n">
+      <x:c r="S49" s="9" t="str">
         <x:v>4814767</x:v>
       </x:c>
       <x:c r="T49" s="10" t="str">
@@ -3553,7 +3625,7 @@
       <x:c r="R50" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S50" s="9" t="n">
+      <x:c r="S50" s="9" t="str">
         <x:v>4814782</x:v>
       </x:c>
       <x:c r="T50" s="10" t="str">
@@ -3617,7 +3689,7 @@
       <x:c r="R51" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S51" s="9" t="n">
+      <x:c r="S51" s="9" t="str">
         <x:v>3731169</x:v>
       </x:c>
       <x:c r="T51" s="10" t="str">
@@ -3681,7 +3753,7 @@
       <x:c r="R52" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S52" s="9" t="n">
+      <x:c r="S52" s="9" t="str">
         <x:v>3742118</x:v>
       </x:c>
       <x:c r="T52" s="10" t="str">
@@ -3745,7 +3817,7 @@
       <x:c r="R53" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S53" s="9" t="n">
+      <x:c r="S53" s="9" t="str">
         <x:v>4528717</x:v>
       </x:c>
       <x:c r="T53" s="10" t="str">
@@ -3809,7 +3881,7 @@
       <x:c r="R54" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S54" s="9" t="n">
+      <x:c r="S54" s="9" t="str">
         <x:v>4528722</x:v>
       </x:c>
       <x:c r="T54" s="10" t="str">
@@ -3873,7 +3945,7 @@
       <x:c r="R55" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S55" s="9" t="n">
+      <x:c r="S55" s="9" t="str">
         <x:v>4528889</x:v>
       </x:c>
       <x:c r="T55" s="10" t="str">
@@ -3941,7 +4013,7 @@
       <x:c r="R56" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S56" s="9" t="n">
+      <x:c r="S56" s="9" t="str">
         <x:v>4529175</x:v>
       </x:c>
       <x:c r="T56" s="10" t="str">
@@ -4007,7 +4079,7 @@
       <x:c r="R57" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S57" s="9" t="n">
+      <x:c r="S57" s="9" t="str">
         <x:v>4529181</x:v>
       </x:c>
       <x:c r="T57" s="10" t="str">
@@ -4071,7 +4143,7 @@
       <x:c r="R58" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S58" s="9" t="n">
+      <x:c r="S58" s="9" t="str">
         <x:v>4815043</x:v>
       </x:c>
       <x:c r="T58" s="10" t="str">
@@ -4135,7 +4207,7 @@
       <x:c r="R59" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S59" s="9" t="n">
+      <x:c r="S59" s="9" t="str">
         <x:v>4815051</x:v>
       </x:c>
       <x:c r="T59" s="10" t="str">
@@ -4190,7 +4262,7 @@
       <x:c r="R60" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S60" s="9" t="n">
+      <x:c r="S60" s="9" t="str">
         <x:v>4330357</x:v>
       </x:c>
       <x:c r="T60" s="10" t="str">
@@ -4245,7 +4317,7 @@
       <x:c r="R61" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S61" s="9" t="n">
+      <x:c r="S61" s="9" t="str">
         <x:v>4330497</x:v>
       </x:c>
       <x:c r="T61" s="10" t="str">
@@ -4300,7 +4372,7 @@
       <x:c r="R62" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S62" s="9" t="n">
+      <x:c r="S62" s="9" t="str">
         <x:v>4814437</x:v>
       </x:c>
       <x:c r="T62" s="10" t="str">
@@ -4355,7 +4427,7 @@
       <x:c r="R63" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S63" s="9" t="n">
+      <x:c r="S63" s="9" t="str">
         <x:v>4814940</x:v>
       </x:c>
       <x:c r="T63" s="10" t="str">
@@ -4416,7 +4488,7 @@
       <x:c r="R64" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S64" s="9" t="n">
+      <x:c r="S64" s="9" t="str">
         <x:v>3741711</x:v>
       </x:c>
       <x:c r="T64" s="10" t="str">
@@ -4477,7 +4549,7 @@
       <x:c r="R65" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S65" s="9" t="n">
+      <x:c r="S65" s="9" t="str">
         <x:v>3741956</x:v>
       </x:c>
       <x:c r="T65" s="10" t="str">
@@ -4538,7 +4610,7 @@
       <x:c r="R66" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S66" s="9" t="n">
+      <x:c r="S66" s="9" t="str">
         <x:v>3741964</x:v>
       </x:c>
       <x:c r="T66" s="10" t="str">
@@ -4599,7 +4671,7 @@
       <x:c r="R67" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S67" s="9" t="n">
+      <x:c r="S67" s="9" t="str">
         <x:v>4324486</x:v>
       </x:c>
       <x:c r="T67" s="10" t="str">
@@ -4660,7 +4732,7 @@
       <x:c r="R68" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S68" s="9" t="n">
+      <x:c r="S68" s="9" t="str">
         <x:v>4324491</x:v>
       </x:c>
       <x:c r="T68" s="10" t="str">
@@ -4721,7 +4793,7 @@
       <x:c r="R69" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S69" s="9" t="n">
+      <x:c r="S69" s="9" t="str">
         <x:v>4330111</x:v>
       </x:c>
       <x:c r="T69" s="10" t="str">
@@ -4782,7 +4854,7 @@
       <x:c r="R70" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S70" s="9" t="n">
+      <x:c r="S70" s="9" t="str">
         <x:v>4330388</x:v>
       </x:c>
       <x:c r="T70" s="10" t="str">
@@ -4843,7 +4915,7 @@
       <x:c r="R71" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S71" s="9" t="n">
+      <x:c r="S71" s="9" t="str">
         <x:v>4330390</x:v>
       </x:c>
       <x:c r="T71" s="10" t="str">
@@ -4904,7 +4976,7 @@
       <x:c r="R72" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S72" s="9" t="n">
+      <x:c r="S72" s="9" t="str">
         <x:v>4528670</x:v>
       </x:c>
       <x:c r="T72" s="10" t="str">
@@ -4965,7 +5037,7 @@
       <x:c r="R73" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S73" s="9" t="n">
+      <x:c r="S73" s="9" t="str">
         <x:v>4528766</x:v>
       </x:c>
       <x:c r="T73" s="10" t="str">
@@ -5026,7 +5098,7 @@
       <x:c r="R74" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S74" s="9" t="n">
+      <x:c r="S74" s="9" t="str">
         <x:v>4814728</x:v>
       </x:c>
       <x:c r="T74" s="10" t="str">
@@ -5087,7 +5159,7 @@
       <x:c r="R75" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S75" s="9" t="n">
+      <x:c r="S75" s="9" t="str">
         <x:v>4814732</x:v>
       </x:c>
       <x:c r="T75" s="10" t="str">
@@ -5148,7 +5220,7 @@
       <x:c r="R76" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S76" s="9" t="n">
+      <x:c r="S76" s="9" t="str">
         <x:v>4814736</x:v>
       </x:c>
       <x:c r="T76" s="10" t="str">
@@ -5209,7 +5281,7 @@
       <x:c r="R77" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S77" s="9" t="n">
+      <x:c r="S77" s="9" t="str">
         <x:v>5154489</x:v>
       </x:c>
       <x:c r="T77" s="10" t="str">
@@ -5271,7 +5343,7 @@
       <x:c r="R78" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S78" s="9" t="n">
+      <x:c r="S78" s="9" t="str">
         <x:v>4324490</x:v>
       </x:c>
       <x:c r="T78" s="10" t="str">
@@ -5339,7 +5411,7 @@
       <x:c r="R79" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S79" s="9" t="n">
+      <x:c r="S79" s="9" t="str">
         <x:v>4330251</x:v>
       </x:c>
       <x:c r="T79" s="10" t="str">
@@ -5400,7 +5472,7 @@
       <x:c r="R80" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S80" s="9" t="n">
+      <x:c r="S80" s="9" t="str">
         <x:v>4330389</x:v>
       </x:c>
       <x:c r="T80" s="10" t="str">
@@ -5461,7 +5533,7 @@
       <x:c r="R81" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S81" s="9" t="n">
+      <x:c r="S81" s="9" t="str">
         <x:v>4814731</x:v>
       </x:c>
       <x:c r="T81" s="10" t="str">
@@ -5522,7 +5594,7 @@
       <x:c r="R82" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S82" s="9" t="n">
+      <x:c r="S82" s="9" t="str">
         <x:v>3789819</x:v>
       </x:c>
       <x:c r="T82" s="10" t="str">
@@ -5583,7 +5655,7 @@
       <x:c r="R83" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S83" s="9" t="n">
+      <x:c r="S83" s="9" t="str">
         <x:v>3789854</x:v>
       </x:c>
       <x:c r="T83" s="10" t="str">
@@ -5644,7 +5716,7 @@
       <x:c r="R84" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S84" s="9" t="n">
+      <x:c r="S84" s="9" t="str">
         <x:v>3790445</x:v>
       </x:c>
       <x:c r="T84" s="10" t="str">
@@ -5705,7 +5777,7 @@
       <x:c r="R85" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S85" s="9" t="n">
+      <x:c r="S85" s="9" t="str">
         <x:v>3790682</x:v>
       </x:c>
       <x:c r="T85" s="10" t="str">
@@ -5766,7 +5838,7 @@
       <x:c r="R86" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S86" s="9" t="n">
+      <x:c r="S86" s="9" t="str">
         <x:v>3790686</x:v>
       </x:c>
       <x:c r="T86" s="10" t="str">
@@ -5827,7 +5899,7 @@
       <x:c r="R87" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S87" s="9" t="n">
+      <x:c r="S87" s="9" t="str">
         <x:v>3790765</x:v>
       </x:c>
       <x:c r="T87" s="10" t="str">
@@ -5888,7 +5960,7 @@
       <x:c r="R88" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S88" s="9" t="n">
+      <x:c r="S88" s="9" t="str">
         <x:v>3790766</x:v>
       </x:c>
       <x:c r="T88" s="10" t="str">
@@ -5949,7 +6021,7 @@
       <x:c r="R89" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S89" s="9" t="n">
+      <x:c r="S89" s="9" t="str">
         <x:v>3790767</x:v>
       </x:c>
       <x:c r="T89" s="10" t="str">
@@ -6010,7 +6082,7 @@
       <x:c r="R90" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S90" s="9" t="n">
+      <x:c r="S90" s="9" t="str">
         <x:v>3790937</x:v>
       </x:c>
       <x:c r="T90" s="10" t="str">
@@ -6071,7 +6143,7 @@
       <x:c r="R91" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S91" s="9" t="n">
+      <x:c r="S91" s="9" t="str">
         <x:v>3791000</x:v>
       </x:c>
       <x:c r="T91" s="10" t="str">
@@ -6132,7 +6204,7 @@
       <x:c r="R92" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S92" s="9" t="n">
+      <x:c r="S92" s="9" t="str">
         <x:v>4528754</x:v>
       </x:c>
       <x:c r="T92" s="10" t="str">
@@ -6193,7 +6265,7 @@
       <x:c r="R93" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S93" s="9" t="n">
+      <x:c r="S93" s="9" t="str">
         <x:v>4814279</x:v>
       </x:c>
       <x:c r="T93" s="10" t="str">
@@ -6254,7 +6326,7 @@
       <x:c r="R94" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S94" s="9" t="n">
+      <x:c r="S94" s="9" t="str">
         <x:v>4814339</x:v>
       </x:c>
       <x:c r="T94" s="10" t="str">
@@ -6315,7 +6387,7 @@
       <x:c r="R95" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S95" s="9" t="n">
+      <x:c r="S95" s="9" t="str">
         <x:v>4814477</x:v>
       </x:c>
       <x:c r="T95" s="10" t="str">
@@ -6376,7 +6448,7 @@
       <x:c r="R96" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S96" s="9" t="n">
+      <x:c r="S96" s="9" t="str">
         <x:v>4814484</x:v>
       </x:c>
       <x:c r="T96" s="10" t="str">
@@ -6437,7 +6509,7 @@
       <x:c r="R97" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S97" s="9" t="n">
+      <x:c r="S97" s="9" t="str">
         <x:v>4814499</x:v>
       </x:c>
       <x:c r="T97" s="10" t="str">
@@ -6498,7 +6570,7 @@
       <x:c r="R98" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S98" s="9" t="n">
+      <x:c r="S98" s="9" t="str">
         <x:v>4814534</x:v>
       </x:c>
       <x:c r="T98" s="10" t="str">
@@ -6559,7 +6631,7 @@
       <x:c r="R99" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S99" s="9" t="n">
+      <x:c r="S99" s="9" t="str">
         <x:v>4814833</x:v>
       </x:c>
       <x:c r="T99" s="10" t="str">
@@ -6620,7 +6692,7 @@
       <x:c r="R100" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S100" s="9" t="n">
+      <x:c r="S100" s="9" t="str">
         <x:v>4814879</x:v>
       </x:c>
       <x:c r="T100" s="10" t="str">
@@ -6681,7 +6753,7 @@
       <x:c r="R101" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S101" s="9" t="n">
+      <x:c r="S101" s="9" t="str">
         <x:v>4814886</x:v>
       </x:c>
       <x:c r="T101" s="10" t="str">
@@ -6742,7 +6814,7 @@
       <x:c r="R102" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S102" s="9" t="n">
+      <x:c r="S102" s="9" t="str">
         <x:v>4814966</x:v>
       </x:c>
       <x:c r="T102" s="10" t="str">
@@ -6803,7 +6875,7 @@
       <x:c r="R103" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S103" s="9" t="n">
+      <x:c r="S103" s="9" t="str">
         <x:v>4815008</x:v>
       </x:c>
       <x:c r="T103" s="10" t="str">
@@ -6867,7 +6939,7 @@
       <x:c r="R104" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S104" s="9" t="n">
+      <x:c r="S104" s="9" t="str">
         <x:v>3731571</x:v>
       </x:c>
       <x:c r="T104" s="10" t="str">
@@ -6931,7 +7003,7 @@
       <x:c r="R105" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S105" s="9" t="n">
+      <x:c r="S105" s="9" t="str">
         <x:v>3741828</x:v>
       </x:c>
       <x:c r="T105" s="10" t="str">
@@ -6995,7 +7067,7 @@
       <x:c r="R106" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S106" s="9" t="n">
+      <x:c r="S106" s="9" t="str">
         <x:v>4324493</x:v>
       </x:c>
       <x:c r="T106" s="10" t="str">
@@ -7059,7 +7131,7 @@
       <x:c r="R107" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S107" s="9" t="n">
+      <x:c r="S107" s="9" t="str">
         <x:v>4324496</x:v>
       </x:c>
       <x:c r="T107" s="10" t="str">
@@ -7123,7 +7195,7 @@
       <x:c r="R108" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S108" s="9" t="n">
+      <x:c r="S108" s="9" t="str">
         <x:v>4330322</x:v>
       </x:c>
       <x:c r="T108" s="10" t="str">
@@ -7187,7 +7259,7 @@
       <x:c r="R109" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S109" s="9" t="n">
+      <x:c r="S109" s="9" t="str">
         <x:v>4814765</x:v>
       </x:c>
       <x:c r="T109" s="10" t="str">
@@ -7251,7 +7323,7 @@
       <x:c r="R110" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S110" s="9" t="n">
+      <x:c r="S110" s="9" t="str">
         <x:v>4528550</x:v>
       </x:c>
       <x:c r="T110" s="10" t="str">
@@ -7315,7 +7387,7 @@
       <x:c r="R111" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S111" s="9" t="n">
+      <x:c r="S111" s="9" t="str">
         <x:v>4528577</x:v>
       </x:c>
       <x:c r="T111" s="10" t="str">
@@ -7379,7 +7451,7 @@
       <x:c r="R112" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S112" s="9" t="n">
+      <x:c r="S112" s="9" t="str">
         <x:v>4529147</x:v>
       </x:c>
       <x:c r="T112" s="10" t="str">
@@ -7443,7 +7515,7 @@
       <x:c r="R113" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S113" s="9" t="n">
+      <x:c r="S113" s="9" t="str">
         <x:v>4814386</x:v>
       </x:c>
       <x:c r="T113" s="10" t="str">
@@ -7507,7 +7579,7 @@
       <x:c r="R114" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S114" s="9" t="n">
+      <x:c r="S114" s="9" t="str">
         <x:v>4814392</x:v>
       </x:c>
       <x:c r="T114" s="10" t="str">
@@ -7571,7 +7643,7 @@
       <x:c r="R115" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S115" s="9" t="n">
+      <x:c r="S115" s="9" t="str">
         <x:v>4814398</x:v>
       </x:c>
       <x:c r="T115" s="10" t="str">
@@ -7635,7 +7707,7 @@
       <x:c r="R116" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S116" s="9" t="n">
+      <x:c r="S116" s="9" t="str">
         <x:v>4814606</x:v>
       </x:c>
       <x:c r="T116" s="10" t="str">
@@ -7699,7 +7771,7 @@
       <x:c r="R117" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S117" s="9" t="n">
+      <x:c r="S117" s="9" t="str">
         <x:v>4815074</x:v>
       </x:c>
       <x:c r="T117" s="10" t="str">
@@ -7763,7 +7835,7 @@
       <x:c r="R118" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S118" s="9" t="n">
+      <x:c r="S118" s="9" t="str">
         <x:v>4815078</x:v>
       </x:c>
       <x:c r="T118" s="10" t="str">
@@ -7818,7 +7890,7 @@
       <x:c r="R119" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S119" s="9" t="n">
+      <x:c r="S119" s="9" t="str">
         <x:v>4330218</x:v>
       </x:c>
       <x:c r="T119" s="10" t="str">
@@ -7873,7 +7945,7 @@
       <x:c r="R120" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S120" s="9" t="n">
+      <x:c r="S120" s="9" t="str">
         <x:v>4330359</x:v>
       </x:c>
       <x:c r="T120" s="10" t="str">
@@ -7933,7 +8005,7 @@
       <x:c r="R121" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S121" s="9" t="n">
+      <x:c r="S121" s="9" t="str">
         <x:v>3731598</x:v>
       </x:c>
       <x:c r="T121" s="10" t="str">
@@ -7988,7 +8060,7 @@
       <x:c r="R122" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S122" s="9" t="n">
+      <x:c r="S122" s="9" t="str">
         <x:v>4814804</x:v>
       </x:c>
       <x:c r="T122" s="10" t="str">
@@ -8043,7 +8115,7 @@
       <x:c r="R123" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S123" s="9" t="n">
+      <x:c r="S123" s="9" t="str">
         <x:v>4815080</x:v>
       </x:c>
       <x:c r="T123" s="10" t="str">
@@ -8104,7 +8176,7 @@
       <x:c r="R124" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S124" s="9" t="n">
+      <x:c r="S124" s="9" t="str">
         <x:v>3741357</x:v>
       </x:c>
       <x:c r="T124" s="10" t="str">
@@ -8165,7 +8237,7 @@
       <x:c r="R125" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S125" s="9" t="n">
+      <x:c r="S125" s="9" t="str">
         <x:v>4324555</x:v>
       </x:c>
       <x:c r="T125" s="10" t="str">
@@ -8226,7 +8298,7 @@
       <x:c r="R126" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S126" s="9" t="n">
+      <x:c r="S126" s="9" t="str">
         <x:v>4330113</x:v>
       </x:c>
       <x:c r="T126" s="10" t="str">
@@ -8287,7 +8359,7 @@
       <x:c r="R127" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S127" s="9" t="n">
+      <x:c r="S127" s="9" t="str">
         <x:v>4330402</x:v>
       </x:c>
       <x:c r="T127" s="10" t="str">
@@ -8348,7 +8420,7 @@
       <x:c r="R128" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S128" s="9" t="n">
+      <x:c r="S128" s="9" t="str">
         <x:v>4330404</x:v>
       </x:c>
       <x:c r="T128" s="10" t="str">
@@ -8409,7 +8481,7 @@
       <x:c r="R129" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S129" s="9" t="n">
+      <x:c r="S129" s="9" t="str">
         <x:v>4528798</x:v>
       </x:c>
       <x:c r="T129" s="10" t="str">
@@ -8470,7 +8542,7 @@
       <x:c r="R130" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S130" s="9" t="n">
+      <x:c r="S130" s="9" t="str">
         <x:v>4324554</x:v>
       </x:c>
       <x:c r="T130" s="10" t="str">
@@ -8531,7 +8603,7 @@
       <x:c r="R131" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S131" s="9" t="n">
+      <x:c r="S131" s="9" t="str">
         <x:v>4330403</x:v>
       </x:c>
       <x:c r="T131" s="10" t="str">
@@ -8592,7 +8664,7 @@
       <x:c r="R132" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S132" s="9" t="n">
+      <x:c r="S132" s="9" t="str">
         <x:v>3769017</x:v>
       </x:c>
       <x:c r="T132" s="10" t="str">
@@ -8653,7 +8725,7 @@
       <x:c r="R133" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S133" s="9" t="n">
+      <x:c r="S133" s="9" t="str">
         <x:v>3786152</x:v>
       </x:c>
       <x:c r="T133" s="10" t="str">
@@ -8714,7 +8786,7 @@
       <x:c r="R134" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S134" s="9" t="n">
+      <x:c r="S134" s="9" t="str">
         <x:v>3789737</x:v>
       </x:c>
       <x:c r="T134" s="10" t="str">
@@ -8775,7 +8847,7 @@
       <x:c r="R135" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S135" s="9" t="n">
+      <x:c r="S135" s="9" t="str">
         <x:v>3790450</x:v>
       </x:c>
       <x:c r="T135" s="10" t="str">
@@ -8836,7 +8908,7 @@
       <x:c r="R136" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S136" s="9" t="n">
+      <x:c r="S136" s="9" t="str">
         <x:v>3790909</x:v>
       </x:c>
       <x:c r="T136" s="10" t="str">
@@ -8897,7 +8969,7 @@
       <x:c r="R137" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S137" s="9" t="n">
+      <x:c r="S137" s="9" t="str">
         <x:v>3790911</x:v>
       </x:c>
       <x:c r="T137" s="10" t="str">
@@ -8958,7 +9030,7 @@
       <x:c r="R138" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S138" s="9" t="n">
+      <x:c r="S138" s="9" t="str">
         <x:v>4528876</x:v>
       </x:c>
       <x:c r="T138" s="10" t="str">
@@ -9019,7 +9091,7 @@
       <x:c r="R139" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S139" s="9" t="n">
+      <x:c r="S139" s="9" t="str">
         <x:v>4814304</x:v>
       </x:c>
       <x:c r="T139" s="10" t="str">
@@ -9080,7 +9152,7 @@
       <x:c r="R140" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S140" s="9" t="n">
+      <x:c r="S140" s="9" t="str">
         <x:v>4814481</x:v>
       </x:c>
       <x:c r="T140" s="10" t="str">
@@ -9141,7 +9213,7 @@
       <x:c r="R141" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S141" s="9" t="n">
+      <x:c r="S141" s="9" t="str">
         <x:v>4814527</x:v>
       </x:c>
       <x:c r="T141" s="10" t="str">
@@ -9202,7 +9274,7 @@
       <x:c r="R142" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S142" s="9" t="n">
+      <x:c r="S142" s="9" t="str">
         <x:v>4814539</x:v>
       </x:c>
       <x:c r="T142" s="10" t="str">
@@ -9263,7 +9335,7 @@
       <x:c r="R143" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S143" s="9" t="n">
+      <x:c r="S143" s="9" t="str">
         <x:v>4814858</x:v>
       </x:c>
       <x:c r="T143" s="10" t="str">
@@ -9325,7 +9397,7 @@
       <x:c r="R144" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S144" s="9" t="n">
+      <x:c r="S144" s="9" t="str">
         <x:v>4815020</x:v>
       </x:c>
       <x:c r="T144" s="10" t="str">
@@ -9386,7 +9458,7 @@
       <x:c r="R145" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S145" s="9" t="n">
+      <x:c r="S145" s="9" t="str">
         <x:v>5096379</x:v>
       </x:c>
       <x:c r="T145" s="10" t="str">
@@ -9447,7 +9519,7 @@
       <x:c r="R146" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S146" s="9" t="n">
+      <x:c r="S146" s="9" t="str">
         <x:v>5098999</x:v>
       </x:c>
       <x:c r="T146" s="10" t="str">
@@ -9511,7 +9583,7 @@
       <x:c r="R147" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S147" s="9" t="n">
+      <x:c r="S147" s="9" t="str">
         <x:v>6900325</x:v>
       </x:c>
       <x:c r="T147" s="10" t="str">
@@ -9566,7 +9638,7 @@
       <x:c r="R148" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S148" s="9" t="n">
+      <x:c r="S148" s="9" t="str">
         <x:v>3731600</x:v>
       </x:c>
       <x:c r="T148" s="10" t="str">
@@ -9621,7 +9693,7 @@
       <x:c r="R149" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S149" s="9" t="n">
+      <x:c r="S149" s="9" t="str">
         <x:v>5099009</x:v>
       </x:c>
       <x:c r="T149" s="10" t="str">
@@ -9676,7 +9748,7 @@
       <x:c r="R150" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S150" s="9" t="n">
+      <x:c r="S150" s="9" t="str">
         <x:v>5098998</x:v>
       </x:c>
       <x:c r="T150" s="10" t="str">
@@ -9740,7 +9812,7 @@
       <x:c r="R151" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S151" s="9" t="n">
+      <x:c r="S151" s="9" t="str">
         <x:v>3731201</x:v>
       </x:c>
       <x:c r="T151" s="10" t="str">
@@ -9804,7 +9876,7 @@
       <x:c r="R152" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S152" s="9" t="n">
+      <x:c r="S152" s="9" t="str">
         <x:v>4330471</x:v>
       </x:c>
       <x:c r="T152" s="10" t="str">
@@ -9868,7 +9940,7 @@
       <x:c r="R153" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S153" s="9" t="n">
+      <x:c r="S153" s="9" t="str">
         <x:v>4814766</x:v>
       </x:c>
       <x:c r="T153" s="10" t="str">
@@ -9932,7 +10004,7 @@
       <x:c r="R154" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S154" s="9" t="n">
+      <x:c r="S154" s="9" t="str">
         <x:v>4814775</x:v>
       </x:c>
       <x:c r="T154" s="10" t="str">
@@ -9996,7 +10068,7 @@
       <x:c r="R155" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S155" s="9" t="n">
+      <x:c r="S155" s="9" t="str">
         <x:v>4529152</x:v>
       </x:c>
       <x:c r="T155" s="10" t="str">
@@ -10060,7 +10132,7 @@
       <x:c r="R156" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S156" s="9" t="n">
+      <x:c r="S156" s="9" t="str">
         <x:v>4528569</x:v>
       </x:c>
       <x:c r="T156" s="10" t="str">
@@ -10124,7 +10196,7 @@
       <x:c r="R157" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S157" s="9" t="n">
+      <x:c r="S157" s="9" t="str">
         <x:v>4528719</x:v>
       </x:c>
       <x:c r="T157" s="10" t="str">
@@ -10188,7 +10260,7 @@
       <x:c r="R158" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S158" s="9" t="n">
+      <x:c r="S158" s="9" t="str">
         <x:v>4529179</x:v>
       </x:c>
       <x:c r="T158" s="10" t="str">
@@ -10257,7 +10329,7 @@
       <x:c r="R159" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S159" s="9" t="n">
+      <x:c r="S159" s="9" t="str">
         <x:v>4529184</x:v>
       </x:c>
       <x:c r="T159" s="10" t="str">
@@ -10321,7 +10393,7 @@
       <x:c r="R160" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S160" s="9" t="n">
+      <x:c r="S160" s="9" t="str">
         <x:v>4811691</x:v>
       </x:c>
       <x:c r="T160" s="10" t="str">
@@ -10385,7 +10457,7 @@
       <x:c r="R161" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S161" s="9" t="n">
+      <x:c r="S161" s="9" t="str">
         <x:v>4814396</x:v>
       </x:c>
       <x:c r="T161" s="10" t="str">
@@ -10449,7 +10521,7 @@
       <x:c r="R162" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S162" s="9" t="n">
+      <x:c r="S162" s="9" t="str">
         <x:v>4815065</x:v>
       </x:c>
       <x:c r="T162" s="10" t="str">
@@ -10517,7 +10589,7 @@
       <x:c r="R163" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S163" s="9" t="n">
+      <x:c r="S163" s="9" t="str">
         <x:v>4815072</x:v>
       </x:c>
       <x:c r="T163" s="10" t="str">
@@ -10581,7 +10653,7 @@
       <x:c r="R164" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S164" s="9" t="n">
+      <x:c r="S164" s="9" t="str">
         <x:v>4815077</x:v>
       </x:c>
       <x:c r="T164" s="10" t="str">
@@ -10646,7 +10718,7 @@
       <x:c r="R165" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S165" s="9" t="n">
+      <x:c r="S165" s="9" t="str">
         <x:v>6900339</x:v>
       </x:c>
       <x:c r="T165" s="10" t="str">
@@ -10710,7 +10782,7 @@
       <x:c r="R166" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S166" s="9" t="n">
+      <x:c r="S166" s="9" t="str">
         <x:v>6900344</x:v>
       </x:c>
       <x:c r="T166" s="10" t="str">
@@ -10765,7 +10837,7 @@
       <x:c r="R167" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S167" s="9" t="n">
+      <x:c r="S167" s="9" t="str">
         <x:v>4330373</x:v>
       </x:c>
       <x:c r="T167" s="10" t="str">
@@ -10820,7 +10892,7 @@
       <x:c r="R168" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S168" s="9" t="n">
+      <x:c r="S168" s="9" t="str">
         <x:v>6900345</x:v>
       </x:c>
       <x:c r="T168" s="10" t="str">
@@ -10875,7 +10947,7 @@
       <x:c r="R169" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S169" s="9" t="n">
+      <x:c r="S169" s="9" t="str">
         <x:v>4814816</x:v>
       </x:c>
       <x:c r="T169" s="10" t="str">
@@ -10930,7 +11002,7 @@
       <x:c r="R170" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S170" s="9" t="n">
+      <x:c r="S170" s="9" t="str">
         <x:v>4814429</x:v>
       </x:c>
       <x:c r="T170" s="10" t="str">
@@ -10991,7 +11063,7 @@
       <x:c r="R171" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S171" s="9" t="n">
+      <x:c r="S171" s="9" t="str">
         <x:v>3731024</x:v>
       </x:c>
       <x:c r="T171" s="10" t="str">
@@ -11052,7 +11124,7 @@
       <x:c r="R172" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S172" s="9" t="n">
+      <x:c r="S172" s="9" t="str">
         <x:v>3741591</x:v>
       </x:c>
       <x:c r="T172" s="10" t="str">
@@ -11113,7 +11185,7 @@
       <x:c r="R173" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S173" s="9" t="n">
+      <x:c r="S173" s="9" t="str">
         <x:v>4324504</x:v>
       </x:c>
       <x:c r="T173" s="10" t="str">
@@ -11174,7 +11246,7 @@
       <x:c r="R174" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S174" s="9" t="n">
+      <x:c r="S174" s="9" t="str">
         <x:v>4324509</x:v>
       </x:c>
       <x:c r="T174" s="10" t="str">
@@ -11235,7 +11307,7 @@
       <x:c r="R175" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S175" s="9" t="n">
+      <x:c r="S175" s="9" t="str">
         <x:v>4330256</x:v>
       </x:c>
       <x:c r="T175" s="10" t="str">
@@ -11296,7 +11368,7 @@
       <x:c r="R176" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S176" s="9" t="n">
+      <x:c r="S176" s="9" t="str">
         <x:v>4330257</x:v>
       </x:c>
       <x:c r="T176" s="10" t="str">
@@ -11357,7 +11429,7 @@
       <x:c r="R177" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S177" s="9" t="n">
+      <x:c r="S177" s="9" t="str">
         <x:v>4814735</x:v>
       </x:c>
       <x:c r="T177" s="10" t="str">
@@ -11418,7 +11490,7 @@
       <x:c r="R178" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S178" s="9" t="n">
+      <x:c r="S178" s="9" t="str">
         <x:v>5154636</x:v>
       </x:c>
       <x:c r="T178" s="10" t="str">
@@ -11482,7 +11554,7 @@
       <x:c r="R179" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S179" s="9" t="n">
+      <x:c r="S179" s="9" t="str">
         <x:v>3741966</x:v>
       </x:c>
       <x:c r="T179" s="10" t="str">
@@ -11543,7 +11615,7 @@
       <x:c r="R180" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S180" s="9" t="n">
+      <x:c r="S180" s="9" t="str">
         <x:v>4324467</x:v>
       </x:c>
       <x:c r="T180" s="10" t="str">
@@ -11604,7 +11676,7 @@
       <x:c r="R181" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S181" s="9" t="n">
+      <x:c r="S181" s="9" t="str">
         <x:v>4330255</x:v>
       </x:c>
       <x:c r="T181" s="10" t="str">
@@ -11665,7 +11737,7 @@
       <x:c r="R182" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S182" s="9" t="n">
+      <x:c r="S182" s="9" t="str">
         <x:v>3789856</x:v>
       </x:c>
       <x:c r="T182" s="10" t="str">
@@ -11726,7 +11798,7 @@
       <x:c r="R183" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S183" s="9" t="n">
+      <x:c r="S183" s="9" t="str">
         <x:v>3790736</x:v>
       </x:c>
       <x:c r="T183" s="10" t="str">
@@ -11787,7 +11859,7 @@
       <x:c r="R184" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S184" s="9" t="n">
+      <x:c r="S184" s="9" t="str">
         <x:v>3790769</x:v>
       </x:c>
       <x:c r="T184" s="10" t="str">
@@ -11848,7 +11920,7 @@
       <x:c r="R185" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S185" s="9" t="n">
+      <x:c r="S185" s="9" t="str">
         <x:v>4529072</x:v>
       </x:c>
       <x:c r="T185" s="10" t="str">
@@ -11910,7 +11982,7 @@
       <x:c r="R186" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S186" s="9" t="n">
+      <x:c r="S186" s="9" t="str">
         <x:v>4529093</x:v>
       </x:c>
       <x:c r="T186" s="10" t="str">
@@ -11971,7 +12043,7 @@
       <x:c r="R187" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S187" s="9" t="n">
+      <x:c r="S187" s="9" t="str">
         <x:v>4814306</x:v>
       </x:c>
       <x:c r="T187" s="10" t="str">
@@ -12032,7 +12104,7 @@
       <x:c r="R188" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S188" s="9" t="n">
+      <x:c r="S188" s="9" t="str">
         <x:v>4814307</x:v>
       </x:c>
       <x:c r="T188" s="10" t="str">
@@ -12093,7 +12165,7 @@
       <x:c r="R189" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S189" s="9" t="n">
+      <x:c r="S189" s="9" t="str">
         <x:v>4814308</x:v>
       </x:c>
       <x:c r="T189" s="10" t="str">
@@ -12154,7 +12226,7 @@
       <x:c r="R190" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S190" s="9" t="n">
+      <x:c r="S190" s="9" t="str">
         <x:v>4814309</x:v>
       </x:c>
       <x:c r="T190" s="10" t="str">
@@ -12215,7 +12287,7 @@
       <x:c r="R191" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S191" s="9" t="n">
+      <x:c r="S191" s="9" t="str">
         <x:v>4814535</x:v>
       </x:c>
       <x:c r="T191" s="10" t="str">
@@ -12276,7 +12348,7 @@
       <x:c r="R192" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S192" s="9" t="n">
+      <x:c r="S192" s="9" t="str">
         <x:v>4814877</x:v>
       </x:c>
       <x:c r="T192" s="10" t="str">
@@ -12337,7 +12409,7 @@
       <x:c r="R193" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S193" s="9" t="n">
+      <x:c r="S193" s="9" t="str">
         <x:v>4815036</x:v>
       </x:c>
       <x:c r="T193" s="10" t="str">
@@ -12392,7 +12464,7 @@
       <x:c r="R194" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S194" s="9" t="n">
+      <x:c r="S194" s="9" t="str">
         <x:v>3731607</x:v>
       </x:c>
       <x:c r="T194" s="10" t="str">
@@ -12460,7 +12532,7 @@
       <x:c r="R195" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S195" s="9" t="n">
+      <x:c r="S195" s="9" t="str">
         <x:v>4324473</x:v>
       </x:c>
       <x:c r="T195" s="10" t="str">
@@ -12524,7 +12596,7 @@
       <x:c r="R196" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S196" s="9" t="n">
+      <x:c r="S196" s="9" t="str">
         <x:v>4324516</x:v>
       </x:c>
       <x:c r="T196" s="10" t="str">
@@ -12588,7 +12660,7 @@
       <x:c r="R197" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S197" s="9" t="n">
+      <x:c r="S197" s="9" t="str">
         <x:v>4324519</x:v>
       </x:c>
       <x:c r="T197" s="10" t="str">
@@ -12652,7 +12724,7 @@
       <x:c r="R198" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S198" s="9" t="n">
+      <x:c r="S198" s="9" t="str">
         <x:v>4330185</x:v>
       </x:c>
       <x:c r="T198" s="10" t="str">
@@ -12717,7 +12789,7 @@
       <x:c r="R199" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S199" s="9" t="n">
+      <x:c r="S199" s="9" t="str">
         <x:v>4330325</x:v>
       </x:c>
       <x:c r="T199" s="10" t="str">
@@ -12781,7 +12853,7 @@
       <x:c r="R200" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S200" s="9" t="n">
+      <x:c r="S200" s="9" t="str">
         <x:v>4814760</x:v>
       </x:c>
       <x:c r="T200" s="10" t="str">
@@ -12845,7 +12917,7 @@
       <x:c r="R201" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S201" s="9" t="n">
+      <x:c r="S201" s="9" t="str">
         <x:v>5154748</x:v>
       </x:c>
       <x:c r="T201" s="10" t="str">
@@ -12909,7 +12981,7 @@
       <x:c r="R202" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S202" s="9" t="n">
+      <x:c r="S202" s="9" t="str">
         <x:v>3791082</x:v>
       </x:c>
       <x:c r="T202" s="10" t="str">
@@ -12973,7 +13045,7 @@
       <x:c r="R203" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S203" s="9" t="n">
+      <x:c r="S203" s="9" t="str">
         <x:v>4528580</x:v>
       </x:c>
       <x:c r="T203" s="10" t="str">
@@ -13037,7 +13109,7 @@
       <x:c r="R204" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S204" s="9" t="n">
+      <x:c r="S204" s="9" t="str">
         <x:v>4528908</x:v>
       </x:c>
       <x:c r="T204" s="10" t="str">
@@ -13104,7 +13176,7 @@
       <x:c r="R205" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S205" s="9" t="n">
+      <x:c r="S205" s="9" t="str">
         <x:v>4529157</x:v>
       </x:c>
       <x:c r="T205" s="10" t="str">
@@ -13168,7 +13240,7 @@
       <x:c r="R206" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S206" s="9" t="n">
+      <x:c r="S206" s="9" t="str">
         <x:v>4814401</x:v>
       </x:c>
       <x:c r="T206" s="10" t="str">
@@ -13232,7 +13304,7 @@
       <x:c r="R207" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S207" s="9" t="n">
+      <x:c r="S207" s="9" t="str">
         <x:v>4814608</x:v>
       </x:c>
       <x:c r="T207" s="10" t="str">
@@ -13296,7 +13368,7 @@
       <x:c r="R208" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S208" s="9" t="n">
+      <x:c r="S208" s="9" t="str">
         <x:v>4814610</x:v>
       </x:c>
       <x:c r="T208" s="10" t="str">
@@ -13360,7 +13432,7 @@
       <x:c r="R209" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S209" s="9" t="n">
+      <x:c r="S209" s="9" t="str">
         <x:v>4814908</x:v>
       </x:c>
       <x:c r="T209" s="10" t="str">
@@ -13431,7 +13503,7 @@
       <x:c r="R210" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S210" s="9" t="n">
+      <x:c r="S210" s="9" t="str">
         <x:v>5099000</x:v>
       </x:c>
       <x:c r="T210" s="10" t="str">
@@ -13503,7 +13575,7 @@
       <x:c r="R211" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S211" s="9" t="n">
+      <x:c r="S211" s="9" t="str">
         <x:v>5099002</x:v>
       </x:c>
       <x:c r="T211" s="10" t="str">
@@ -13567,7 +13639,7 @@
       <x:c r="R212" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S212" s="9" t="n">
+      <x:c r="S212" s="9" t="str">
         <x:v>5099003</x:v>
       </x:c>
       <x:c r="T212" s="10" t="str">
@@ -13622,7 +13694,7 @@
       <x:c r="R213" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S213" s="9" t="n">
+      <x:c r="S213" s="9" t="str">
         <x:v>4324529</x:v>
       </x:c>
       <x:c r="T213" s="10" t="str">
@@ -13677,7 +13749,7 @@
       <x:c r="R214" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S214" s="9" t="n">
+      <x:c r="S214" s="9" t="str">
         <x:v>4324530</x:v>
       </x:c>
       <x:c r="T214" s="10" t="str">
@@ -13732,7 +13804,7 @@
       <x:c r="R215" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S215" s="9" t="n">
+      <x:c r="S215" s="9" t="str">
         <x:v>4330360</x:v>
       </x:c>
       <x:c r="T215" s="10" t="str">
@@ -13787,7 +13859,7 @@
       <x:c r="R216" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S216" s="9" t="n">
+      <x:c r="S216" s="9" t="str">
         <x:v>4330503</x:v>
       </x:c>
       <x:c r="T216" s="10" t="str">
@@ -13842,7 +13914,7 @@
       <x:c r="R217" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S217" s="9" t="n">
+      <x:c r="S217" s="9" t="str">
         <x:v>4814803</x:v>
       </x:c>
       <x:c r="T217" s="10" t="str">
@@ -13897,7 +13969,7 @@
       <x:c r="R218" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S218" s="9" t="n">
+      <x:c r="S218" s="9" t="str">
         <x:v>4814426</x:v>
       </x:c>
       <x:c r="T218" s="10" t="str">
@@ -13960,7 +14032,7 @@
       <x:c r="R219" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S219" s="9" t="n">
+      <x:c r="S219" s="9" t="str">
         <x:v>3741607</x:v>
       </x:c>
       <x:c r="T219" s="10" t="str">
@@ -14021,7 +14093,7 @@
       <x:c r="R220" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S220" s="9" t="n">
+      <x:c r="S220" s="9" t="str">
         <x:v>4324583</x:v>
       </x:c>
       <x:c r="T220" s="10" t="str">
@@ -14082,7 +14154,7 @@
       <x:c r="R221" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S221" s="9" t="n">
+      <x:c r="S221" s="9" t="str">
         <x:v>4324599</x:v>
       </x:c>
       <x:c r="T221" s="10" t="str">
@@ -14143,7 +14215,7 @@
       <x:c r="R222" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S222" s="9" t="n">
+      <x:c r="S222" s="9" t="str">
         <x:v>4324600</x:v>
       </x:c>
       <x:c r="T222" s="10" t="str">
@@ -14204,7 +14276,7 @@
       <x:c r="R223" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S223" s="9" t="n">
+      <x:c r="S223" s="9" t="str">
         <x:v>4330128</x:v>
       </x:c>
       <x:c r="T223" s="10" t="str">
@@ -14265,7 +14337,7 @@
       <x:c r="R224" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S224" s="9" t="n">
+      <x:c r="S224" s="9" t="str">
         <x:v>4330130</x:v>
       </x:c>
       <x:c r="T224" s="10" t="str">
@@ -14326,7 +14398,7 @@
       <x:c r="R225" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S225" s="9" t="n">
+      <x:c r="S225" s="9" t="str">
         <x:v>4330132</x:v>
       </x:c>
       <x:c r="T225" s="10" t="str">
@@ -14387,7 +14459,7 @@
       <x:c r="R226" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S226" s="9" t="n">
+      <x:c r="S226" s="9" t="str">
         <x:v>4330133</x:v>
       </x:c>
       <x:c r="T226" s="10" t="str">
@@ -14448,7 +14520,7 @@
       <x:c r="R227" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S227" s="9" t="n">
+      <x:c r="S227" s="9" t="str">
         <x:v>4330167</x:v>
       </x:c>
       <x:c r="T227" s="10" t="str">
@@ -14509,7 +14581,7 @@
       <x:c r="R228" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S228" s="9" t="n">
+      <x:c r="S228" s="9" t="str">
         <x:v>4330264</x:v>
       </x:c>
       <x:c r="T228" s="10" t="str">
@@ -14570,7 +14642,7 @@
       <x:c r="R229" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S229" s="9" t="n">
+      <x:c r="S229" s="9" t="str">
         <x:v>4330265</x:v>
       </x:c>
       <x:c r="T229" s="10" t="str">
@@ -14631,7 +14703,7 @@
       <x:c r="R230" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S230" s="9" t="n">
+      <x:c r="S230" s="9" t="str">
         <x:v>4330266</x:v>
       </x:c>
       <x:c r="T230" s="10" t="str">
@@ -14692,7 +14764,7 @@
       <x:c r="R231" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S231" s="9" t="n">
+      <x:c r="S231" s="9" t="str">
         <x:v>4330267</x:v>
       </x:c>
       <x:c r="T231" s="10" t="str">
@@ -14753,7 +14825,7 @@
       <x:c r="R232" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S232" s="9" t="n">
+      <x:c r="S232" s="9" t="str">
         <x:v>4330268</x:v>
       </x:c>
       <x:c r="T232" s="10" t="str">
@@ -14814,7 +14886,7 @@
       <x:c r="R233" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S233" s="9" t="n">
+      <x:c r="S233" s="9" t="str">
         <x:v>4330408</x:v>
       </x:c>
       <x:c r="T233" s="10" t="str">
@@ -14875,7 +14947,7 @@
       <x:c r="R234" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S234" s="9" t="n">
+      <x:c r="S234" s="9" t="str">
         <x:v>4330410</x:v>
       </x:c>
       <x:c r="T234" s="10" t="str">
@@ -14936,7 +15008,7 @@
       <x:c r="R235" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S235" s="9" t="n">
+      <x:c r="S235" s="9" t="str">
         <x:v>4330415</x:v>
       </x:c>
       <x:c r="T235" s="10" t="str">
@@ -14997,7 +15069,7 @@
       <x:c r="R236" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S236" s="9" t="n">
+      <x:c r="S236" s="9" t="str">
         <x:v>4814680</x:v>
       </x:c>
       <x:c r="T236" s="10" t="str">
@@ -15058,7 +15130,7 @@
       <x:c r="R237" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S237" s="9" t="n">
+      <x:c r="S237" s="9" t="str">
         <x:v>4814683</x:v>
       </x:c>
       <x:c r="T237" s="10" t="str">
@@ -15119,7 +15191,7 @@
       <x:c r="R238" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S238" s="9" t="n">
+      <x:c r="S238" s="9" t="str">
         <x:v>4814686</x:v>
       </x:c>
       <x:c r="T238" s="10" t="str">
@@ -15180,7 +15252,7 @@
       <x:c r="R239" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S239" s="9" t="n">
+      <x:c r="S239" s="9" t="str">
         <x:v>4814699</x:v>
       </x:c>
       <x:c r="T239" s="10" t="str">
@@ -15241,7 +15313,7 @@
       <x:c r="R240" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S240" s="9" t="n">
+      <x:c r="S240" s="9" t="str">
         <x:v>4814705</x:v>
       </x:c>
       <x:c r="T240" s="10" t="str">
@@ -15302,7 +15374,7 @@
       <x:c r="R241" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S241" s="9" t="n">
+      <x:c r="S241" s="9" t="str">
         <x:v>4814730</x:v>
       </x:c>
       <x:c r="T241" s="10" t="str">
@@ -15363,7 +15435,7 @@
       <x:c r="R242" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S242" s="9" t="n">
+      <x:c r="S242" s="9" t="str">
         <x:v>5154383</x:v>
       </x:c>
       <x:c r="T242" s="10" t="str">
@@ -15424,7 +15496,7 @@
       <x:c r="R243" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S243" s="9" t="n">
+      <x:c r="S243" s="9" t="str">
         <x:v>5154939</x:v>
       </x:c>
       <x:c r="T243" s="10" t="str">
@@ -15485,7 +15557,7 @@
       <x:c r="R244" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S244" s="9" t="n">
+      <x:c r="S244" s="9" t="str">
         <x:v>5154941</x:v>
       </x:c>
       <x:c r="T244" s="10" t="str">
@@ -15546,7 +15618,7 @@
       <x:c r="R245" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S245" s="9" t="n">
+      <x:c r="S245" s="9" t="str">
         <x:v>4324601</x:v>
       </x:c>
       <x:c r="T245" s="10" t="str">
@@ -15607,7 +15679,7 @@
       <x:c r="R246" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S246" s="9" t="n">
+      <x:c r="S246" s="9" t="str">
         <x:v>4330127</x:v>
       </x:c>
       <x:c r="T246" s="10" t="str">
@@ -15668,7 +15740,7 @@
       <x:c r="R247" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S247" s="9" t="n">
+      <x:c r="S247" s="9" t="str">
         <x:v>4528530</x:v>
       </x:c>
       <x:c r="T247" s="10" t="str">
@@ -15729,7 +15801,7 @@
       <x:c r="R248" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S248" s="9" t="n">
+      <x:c r="S248" s="9" t="str">
         <x:v>4528792</x:v>
       </x:c>
       <x:c r="T248" s="10" t="str">
@@ -15790,7 +15862,7 @@
       <x:c r="R249" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S249" s="9" t="n">
+      <x:c r="S249" s="9" t="str">
         <x:v>4811604</x:v>
       </x:c>
       <x:c r="T249" s="10" t="str">
@@ -15851,7 +15923,7 @@
       <x:c r="R250" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S250" s="9" t="n">
+      <x:c r="S250" s="9" t="str">
         <x:v>4814295</x:v>
       </x:c>
       <x:c r="T250" s="10" t="str">
@@ -15912,7 +15984,7 @@
       <x:c r="R251" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S251" s="9" t="n">
+      <x:c r="S251" s="9" t="str">
         <x:v>4814296</x:v>
       </x:c>
       <x:c r="T251" s="10" t="str">
@@ -15973,7 +16045,7 @@
       <x:c r="R252" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S252" s="9" t="n">
+      <x:c r="S252" s="9" t="str">
         <x:v>4814312</x:v>
       </x:c>
       <x:c r="T252" s="10" t="str">
@@ -16034,7 +16106,7 @@
       <x:c r="R253" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S253" s="9" t="n">
+      <x:c r="S253" s="9" t="str">
         <x:v>4814340</x:v>
       </x:c>
       <x:c r="T253" s="10" t="str">
@@ -16095,7 +16167,7 @@
       <x:c r="R254" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S254" s="9" t="n">
+      <x:c r="S254" s="9" t="str">
         <x:v>4814341</x:v>
       </x:c>
       <x:c r="T254" s="10" t="str">
@@ -16156,7 +16228,7 @@
       <x:c r="R255" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S255" s="9" t="n">
+      <x:c r="S255" s="9" t="str">
         <x:v>4814470</x:v>
       </x:c>
       <x:c r="T255" s="10" t="str">
@@ -16217,7 +16289,7 @@
       <x:c r="R256" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S256" s="9" t="n">
+      <x:c r="S256" s="9" t="str">
         <x:v>4814502</x:v>
       </x:c>
       <x:c r="T256" s="10" t="str">
@@ -16278,7 +16350,7 @@
       <x:c r="R257" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S257" s="9" t="n">
+      <x:c r="S257" s="9" t="str">
         <x:v>4814503</x:v>
       </x:c>
       <x:c r="T257" s="10" t="str">
@@ -16339,7 +16411,7 @@
       <x:c r="R258" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S258" s="9" t="n">
+      <x:c r="S258" s="9" t="str">
         <x:v>4814515</x:v>
       </x:c>
       <x:c r="T258" s="10" t="str">
@@ -16400,7 +16472,7 @@
       <x:c r="R259" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S259" s="9" t="n">
+      <x:c r="S259" s="9" t="str">
         <x:v>4814528</x:v>
       </x:c>
       <x:c r="T259" s="10" t="str">
@@ -16461,7 +16533,7 @@
       <x:c r="R260" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S260" s="9" t="n">
+      <x:c r="S260" s="9" t="str">
         <x:v>4814530</x:v>
       </x:c>
       <x:c r="T260" s="10" t="str">
@@ -16522,7 +16594,7 @@
       <x:c r="R261" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S261" s="9" t="n">
+      <x:c r="S261" s="9" t="str">
         <x:v>4814541</x:v>
       </x:c>
       <x:c r="T261" s="10" t="str">
@@ -16583,7 +16655,7 @@
       <x:c r="R262" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S262" s="9" t="n">
+      <x:c r="S262" s="9" t="str">
         <x:v>4814835</x:v>
       </x:c>
       <x:c r="T262" s="10" t="str">
@@ -16644,7 +16716,7 @@
       <x:c r="R263" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S263" s="9" t="n">
+      <x:c r="S263" s="9" t="str">
         <x:v>4814836</x:v>
       </x:c>
       <x:c r="T263" s="10" t="str">
@@ -16705,7 +16777,7 @@
       <x:c r="R264" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S264" s="9" t="n">
+      <x:c r="S264" s="9" t="str">
         <x:v>4814869</x:v>
       </x:c>
       <x:c r="T264" s="10" t="str">
@@ -16766,7 +16838,7 @@
       <x:c r="R265" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S265" s="9" t="n">
+      <x:c r="S265" s="9" t="str">
         <x:v>4814873</x:v>
       </x:c>
       <x:c r="T265" s="10" t="str">
@@ -16827,7 +16899,7 @@
       <x:c r="R266" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S266" s="9" t="n">
+      <x:c r="S266" s="9" t="str">
         <x:v>4814896</x:v>
       </x:c>
       <x:c r="T266" s="10" t="str">
@@ -16888,7 +16960,7 @@
       <x:c r="R267" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S267" s="9" t="n">
+      <x:c r="S267" s="9" t="str">
         <x:v>4815014</x:v>
       </x:c>
       <x:c r="T267" s="10" t="str">
@@ -16949,7 +17021,7 @@
       <x:c r="R268" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S268" s="9" t="n">
+      <x:c r="S268" s="9" t="str">
         <x:v>4815015</x:v>
       </x:c>
       <x:c r="T268" s="10" t="str">
@@ -17010,7 +17082,7 @@
       <x:c r="R269" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S269" s="9" t="n">
+      <x:c r="S269" s="9" t="str">
         <x:v>4815016</x:v>
       </x:c>
       <x:c r="T269" s="10" t="str">
@@ -17071,7 +17143,7 @@
       <x:c r="R270" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S270" s="9" t="n">
+      <x:c r="S270" s="9" t="str">
         <x:v>4815039</x:v>
       </x:c>
       <x:c r="T270" s="10" t="str">
@@ -17135,7 +17207,7 @@
       <x:c r="R271" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S271" s="9" t="n">
+      <x:c r="S271" s="9" t="str">
         <x:v>3731193</x:v>
       </x:c>
       <x:c r="T271" s="10" t="str">
@@ -17199,7 +17271,7 @@
       <x:c r="R272" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S272" s="9" t="n">
+      <x:c r="S272" s="9" t="str">
         <x:v>4324471</x:v>
       </x:c>
       <x:c r="T272" s="10" t="str">
@@ -17263,7 +17335,7 @@
       <x:c r="R273" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S273" s="9" t="n">
+      <x:c r="S273" s="9" t="str">
         <x:v>4324594</x:v>
       </x:c>
       <x:c r="T273" s="10" t="str">
@@ -17327,7 +17399,7 @@
       <x:c r="R274" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S274" s="9" t="n">
+      <x:c r="S274" s="9" t="str">
         <x:v>4330189</x:v>
       </x:c>
       <x:c r="T274" s="10" t="str">
@@ -17391,7 +17463,7 @@
       <x:c r="R275" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S275" s="9" t="n">
+      <x:c r="S275" s="9" t="str">
         <x:v>4330210</x:v>
       </x:c>
       <x:c r="T275" s="10" t="str">
@@ -17456,7 +17528,7 @@
       <x:c r="R276" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S276" s="9" t="n">
+      <x:c r="S276" s="9" t="str">
         <x:v>4814783</x:v>
       </x:c>
       <x:c r="T276" s="10" t="str">
@@ -17520,7 +17592,7 @@
       <x:c r="R277" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S277" s="9" t="n">
+      <x:c r="S277" s="9" t="str">
         <x:v>4330473</x:v>
       </x:c>
       <x:c r="T277" s="10" t="str">
@@ -17584,7 +17656,7 @@
       <x:c r="R278" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S278" s="9" t="n">
+      <x:c r="S278" s="9" t="str">
         <x:v>4330474</x:v>
       </x:c>
       <x:c r="T278" s="10" t="str">
@@ -17648,7 +17720,7 @@
       <x:c r="R279" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S279" s="9" t="n">
+      <x:c r="S279" s="9" t="str">
         <x:v>5086683</x:v>
       </x:c>
       <x:c r="T279" s="10" t="str">
@@ -17712,7 +17784,7 @@
       <x:c r="R280" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S280" s="9" t="n">
+      <x:c r="S280" s="9" t="str">
         <x:v>5099010</x:v>
       </x:c>
       <x:c r="T280" s="10" t="str">
@@ -17776,7 +17848,7 @@
       <x:c r="R281" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S281" s="9" t="n">
+      <x:c r="S281" s="9" t="str">
         <x:v>3790592</x:v>
       </x:c>
       <x:c r="T281" s="10" t="str">
@@ -17840,7 +17912,7 @@
       <x:c r="R282" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S282" s="9" t="n">
+      <x:c r="S282" s="9" t="str">
         <x:v>3791065</x:v>
       </x:c>
       <x:c r="T282" s="10" t="str">
@@ -17904,7 +17976,7 @@
       <x:c r="R283" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S283" s="9" t="n">
+      <x:c r="S283" s="9" t="str">
         <x:v>4528559</x:v>
       </x:c>
       <x:c r="T283" s="10" t="str">
@@ -17969,7 +18041,7 @@
       <x:c r="R284" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S284" s="9" t="n">
+      <x:c r="S284" s="9" t="str">
         <x:v>4529149</x:v>
       </x:c>
       <x:c r="T284" s="10" t="str">
@@ -18033,7 +18105,7 @@
       <x:c r="R285" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S285" s="9" t="n">
+      <x:c r="S285" s="9" t="str">
         <x:v>4814387</x:v>
       </x:c>
       <x:c r="T285" s="10" t="str">
@@ -18097,7 +18169,7 @@
       <x:c r="R286" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S286" s="9" t="n">
+      <x:c r="S286" s="9" t="str">
         <x:v>4814578</x:v>
       </x:c>
       <x:c r="T286" s="10" t="str">
@@ -18161,7 +18233,7 @@
       <x:c r="R287" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S287" s="9" t="n">
+      <x:c r="S287" s="9" t="str">
         <x:v>4814584</x:v>
       </x:c>
       <x:c r="T287" s="10" t="str">
@@ -18225,7 +18297,7 @@
       <x:c r="R288" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S288" s="9" t="n">
+      <x:c r="S288" s="9" t="str">
         <x:v>4814617</x:v>
       </x:c>
       <x:c r="T288" s="10" t="str">
@@ -18289,7 +18361,7 @@
       <x:c r="R289" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S289" s="9" t="n">
+      <x:c r="S289" s="9" t="str">
         <x:v>4814622</x:v>
       </x:c>
       <x:c r="T289" s="10" t="str">
@@ -18353,7 +18425,7 @@
       <x:c r="R290" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S290" s="9" t="n">
+      <x:c r="S290" s="9" t="str">
         <x:v>4814623</x:v>
       </x:c>
       <x:c r="T290" s="10" t="str">
@@ -18417,7 +18489,7 @@
       <x:c r="R291" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S291" s="9" t="n">
+      <x:c r="S291" s="9" t="str">
         <x:v>4814938</x:v>
       </x:c>
       <x:c r="T291" s="10" t="str">
@@ -18483,7 +18555,7 @@
       <x:c r="R292" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S292" s="9" t="n">
+      <x:c r="S292" s="9" t="str">
         <x:v>4815048</x:v>
       </x:c>
       <x:c r="T292" s="10" t="str">
@@ -18547,7 +18619,7 @@
       <x:c r="R293" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S293" s="9" t="n">
+      <x:c r="S293" s="9" t="str">
         <x:v>4815061</x:v>
       </x:c>
       <x:c r="T293" s="10" t="str">
@@ -18611,7 +18683,7 @@
       <x:c r="R294" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S294" s="9" t="n">
+      <x:c r="S294" s="9" t="str">
         <x:v>4815062</x:v>
       </x:c>
       <x:c r="T294" s="10" t="str">
@@ -18675,7 +18747,7 @@
       <x:c r="R295" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S295" s="9" t="n">
+      <x:c r="S295" s="9" t="str">
         <x:v>4815064</x:v>
       </x:c>
       <x:c r="T295" s="10" t="str">
@@ -18739,7 +18811,7 @@
       <x:c r="R296" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S296" s="9" t="n">
+      <x:c r="S296" s="9" t="str">
         <x:v>5099004</x:v>
       </x:c>
       <x:c r="T296" s="10" t="str">
@@ -18794,7 +18866,7 @@
       <x:c r="R297" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S297" s="9" t="n">
+      <x:c r="S297" s="9" t="str">
         <x:v>4324598</x:v>
       </x:c>
       <x:c r="T297" s="10" t="str">
@@ -18849,7 +18921,7 @@
       <x:c r="R298" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S298" s="9" t="n">
+      <x:c r="S298" s="9" t="str">
         <x:v>4330375</x:v>
       </x:c>
       <x:c r="T298" s="10" t="str">
@@ -18904,7 +18976,7 @@
       <x:c r="R299" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S299" s="9" t="n">
+      <x:c r="S299" s="9" t="str">
         <x:v>4814815</x:v>
       </x:c>
       <x:c r="T299" s="10" t="str">
@@ -18959,7 +19031,7 @@
       <x:c r="R300" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S300" s="9" t="n">
+      <x:c r="S300" s="9" t="str">
         <x:v>4814430</x:v>
       </x:c>
       <x:c r="T300" s="10" t="str">
@@ -19014,7 +19086,7 @@
       <x:c r="R301" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S301" s="9" t="n">
+      <x:c r="S301" s="9" t="str">
         <x:v>4815086</x:v>
       </x:c>
       <x:c r="T301" s="10" t="str">
@@ -19069,7 +19141,7 @@
       <x:c r="R302" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S302" s="9" t="n">
+      <x:c r="S302" s="9" t="str">
         <x:v>4815090</x:v>
       </x:c>
       <x:c r="T302" s="10" t="str">
@@ -19124,7 +19196,7 @@
       <x:c r="R303" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S303" s="9" t="n">
+      <x:c r="S303" s="9" t="str">
         <x:v>4815098</x:v>
       </x:c>
       <x:c r="T303" s="10" t="str">
@@ -19185,7 +19257,7 @@
       <x:c r="R304" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S304" s="9" t="n">
+      <x:c r="S304" s="9" t="str">
         <x:v>3731091</x:v>
       </x:c>
       <x:c r="T304" s="10" t="str">
@@ -19246,7 +19318,7 @@
       <x:c r="R305" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S305" s="9" t="n">
+      <x:c r="S305" s="9" t="str">
         <x:v>3731092</x:v>
       </x:c>
       <x:c r="T305" s="10" t="str">
@@ -19307,7 +19379,7 @@
       <x:c r="R306" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S306" s="9" t="n">
+      <x:c r="S306" s="9" t="str">
         <x:v>3731383</x:v>
       </x:c>
       <x:c r="T306" s="10" t="str">
@@ -19368,7 +19440,7 @@
       <x:c r="R307" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S307" s="9" t="n">
+      <x:c r="S307" s="9" t="str">
         <x:v>3741618</x:v>
       </x:c>
       <x:c r="T307" s="10" t="str">
@@ -19429,7 +19501,7 @@
       <x:c r="R308" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S308" s="9" t="n">
+      <x:c r="S308" s="9" t="str">
         <x:v>3741681</x:v>
       </x:c>
       <x:c r="T308" s="10" t="str">
@@ -19490,7 +19562,7 @@
       <x:c r="R309" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S309" s="9" t="n">
+      <x:c r="S309" s="9" t="str">
         <x:v>3741683</x:v>
       </x:c>
       <x:c r="T309" s="10" t="str">
@@ -19551,7 +19623,7 @@
       <x:c r="R310" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S310" s="9" t="n">
+      <x:c r="S310" s="9" t="str">
         <x:v>3741995</x:v>
       </x:c>
       <x:c r="T310" s="10" t="str">
@@ -19612,7 +19684,7 @@
       <x:c r="R311" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S311" s="9" t="n">
+      <x:c r="S311" s="9" t="str">
         <x:v>3742036</x:v>
       </x:c>
       <x:c r="T311" s="10" t="str">
@@ -19673,7 +19745,7 @@
       <x:c r="R312" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S312" s="9" t="n">
+      <x:c r="S312" s="9" t="str">
         <x:v>4324617</x:v>
       </x:c>
       <x:c r="T312" s="10" t="str">
@@ -19734,7 +19806,7 @@
       <x:c r="R313" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S313" s="9" t="n">
+      <x:c r="S313" s="9" t="str">
         <x:v>4324619</x:v>
       </x:c>
       <x:c r="T313" s="10" t="str">
@@ -19795,7 +19867,7 @@
       <x:c r="R314" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S314" s="9" t="n">
+      <x:c r="S314" s="9" t="str">
         <x:v>4324620</x:v>
       </x:c>
       <x:c r="T314" s="10" t="str">
@@ -19856,7 +19928,7 @@
       <x:c r="R315" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S315" s="9" t="n">
+      <x:c r="S315" s="9" t="str">
         <x:v>4324624</x:v>
       </x:c>
       <x:c r="T315" s="10" t="str">
@@ -19917,7 +19989,7 @@
       <x:c r="R316" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S316" s="9" t="n">
+      <x:c r="S316" s="9" t="str">
         <x:v>4324625</x:v>
       </x:c>
       <x:c r="T316" s="10" t="str">
@@ -19978,7 +20050,7 @@
       <x:c r="R317" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S317" s="9" t="n">
+      <x:c r="S317" s="9" t="str">
         <x:v>4324626</x:v>
       </x:c>
       <x:c r="T317" s="10" t="str">
@@ -20045,7 +20117,7 @@
       <x:c r="R318" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S318" s="9" t="n">
+      <x:c r="S318" s="9" t="str">
         <x:v>4324628</x:v>
       </x:c>
       <x:c r="T318" s="10" t="str">
@@ -20106,7 +20178,7 @@
       <x:c r="R319" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S319" s="9" t="n">
+      <x:c r="S319" s="9" t="str">
         <x:v>4330143</x:v>
       </x:c>
       <x:c r="T319" s="10" t="str">
@@ -20167,7 +20239,7 @@
       <x:c r="R320" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S320" s="9" t="n">
+      <x:c r="S320" s="9" t="str">
         <x:v>4330280</x:v>
       </x:c>
       <x:c r="T320" s="10" t="str">
@@ -20228,7 +20300,7 @@
       <x:c r="R321" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S321" s="9" t="n">
+      <x:c r="S321" s="9" t="str">
         <x:v>4330284</x:v>
       </x:c>
       <x:c r="T321" s="10" t="str">
@@ -20289,7 +20361,7 @@
       <x:c r="R322" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S322" s="9" t="n">
+      <x:c r="S322" s="9" t="str">
         <x:v>4330420</x:v>
       </x:c>
       <x:c r="T322" s="10" t="str">
@@ -20350,7 +20422,7 @@
       <x:c r="R323" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S323" s="9" t="n">
+      <x:c r="S323" s="9" t="str">
         <x:v>4330421</x:v>
       </x:c>
       <x:c r="T323" s="10" t="str">
@@ -20411,7 +20483,7 @@
       <x:c r="R324" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S324" s="9" t="n">
+      <x:c r="S324" s="9" t="str">
         <x:v>4330422</x:v>
       </x:c>
       <x:c r="T324" s="10" t="str">
@@ -20472,7 +20544,7 @@
       <x:c r="R325" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S325" s="9" t="n">
+      <x:c r="S325" s="9" t="str">
         <x:v>4330428</x:v>
       </x:c>
       <x:c r="T325" s="10" t="str">
@@ -20533,7 +20605,7 @@
       <x:c r="R326" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S326" s="9" t="n">
+      <x:c r="S326" s="9" t="str">
         <x:v>4814704</x:v>
       </x:c>
       <x:c r="T326" s="10" t="str">
@@ -20594,7 +20666,7 @@
       <x:c r="R327" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S327" s="9" t="n">
+      <x:c r="S327" s="9" t="str">
         <x:v>4814725</x:v>
       </x:c>
       <x:c r="T327" s="10" t="str">
@@ -20655,7 +20727,7 @@
       <x:c r="R328" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S328" s="9" t="n">
+      <x:c r="S328" s="9" t="str">
         <x:v>4814743</x:v>
       </x:c>
       <x:c r="T328" s="10" t="str">
@@ -20716,7 +20788,7 @@
       <x:c r="R329" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S329" s="9" t="n">
+      <x:c r="S329" s="9" t="str">
         <x:v>5087840</x:v>
       </x:c>
       <x:c r="T329" s="10" t="str">
@@ -20777,7 +20849,7 @@
       <x:c r="R330" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S330" s="9" t="n">
+      <x:c r="S330" s="9" t="str">
         <x:v>3731088</x:v>
       </x:c>
       <x:c r="T330" s="10" t="str">
@@ -20838,7 +20910,7 @@
       <x:c r="R331" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S331" s="9" t="n">
+      <x:c r="S331" s="9" t="str">
         <x:v>3741380</x:v>
       </x:c>
       <x:c r="T331" s="10" t="str">
@@ -20899,7 +20971,7 @@
       <x:c r="R332" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S332" s="9" t="n">
+      <x:c r="S332" s="9" t="str">
         <x:v>3742042</x:v>
       </x:c>
       <x:c r="T332" s="10" t="str">
@@ -20960,7 +21032,7 @@
       <x:c r="R333" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S333" s="9" t="n">
+      <x:c r="S333" s="9" t="str">
         <x:v>3742045</x:v>
       </x:c>
       <x:c r="T333" s="10" t="str">
@@ -21021,7 +21093,7 @@
       <x:c r="R334" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S334" s="9" t="n">
+      <x:c r="S334" s="9" t="str">
         <x:v>5154819</x:v>
       </x:c>
       <x:c r="T334" s="10" t="str">
@@ -21085,7 +21157,7 @@
       <x:c r="R335" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S335" s="9" t="n">
+      <x:c r="S335" s="9" t="str">
         <x:v>6900403</x:v>
       </x:c>
       <x:c r="T335" s="10" t="str">
@@ -21146,7 +21218,7 @@
       <x:c r="R336" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S336" s="9" t="n">
+      <x:c r="S336" s="9" t="str">
         <x:v>3768970</x:v>
       </x:c>
       <x:c r="T336" s="10" t="str">
@@ -21207,7 +21279,7 @@
       <x:c r="R337" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S337" s="9" t="n">
+      <x:c r="S337" s="9" t="str">
         <x:v>3769001</x:v>
       </x:c>
       <x:c r="T337" s="10" t="str">
@@ -21268,7 +21340,7 @@
       <x:c r="R338" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S338" s="9" t="n">
+      <x:c r="S338" s="9" t="str">
         <x:v>3769005</x:v>
       </x:c>
       <x:c r="T338" s="10" t="str">
@@ -21329,7 +21401,7 @@
       <x:c r="R339" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S339" s="9" t="n">
+      <x:c r="S339" s="9" t="str">
         <x:v>3769036</x:v>
       </x:c>
       <x:c r="T339" s="10" t="str">
@@ -21390,7 +21462,7 @@
       <x:c r="R340" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S340" s="9" t="n">
+      <x:c r="S340" s="9" t="str">
         <x:v>3787760</x:v>
       </x:c>
       <x:c r="T340" s="10" t="str">
@@ -21451,7 +21523,7 @@
       <x:c r="R341" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S341" s="9" t="n">
+      <x:c r="S341" s="9" t="str">
         <x:v>3787790</x:v>
       </x:c>
       <x:c r="T341" s="10" t="str">
@@ -21512,7 +21584,7 @@
       <x:c r="R342" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S342" s="9" t="n">
+      <x:c r="S342" s="9" t="str">
         <x:v>3789745</x:v>
       </x:c>
       <x:c r="T342" s="10" t="str">
@@ -21573,7 +21645,7 @@
       <x:c r="R343" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S343" s="9" t="n">
+      <x:c r="S343" s="9" t="str">
         <x:v>3789746</x:v>
       </x:c>
       <x:c r="T343" s="10" t="str">
@@ -21634,7 +21706,7 @@
       <x:c r="R344" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S344" s="9" t="n">
+      <x:c r="S344" s="9" t="str">
         <x:v>3789803</x:v>
       </x:c>
       <x:c r="T344" s="10" t="str">
@@ -21695,7 +21767,7 @@
       <x:c r="R345" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S345" s="9" t="n">
+      <x:c r="S345" s="9" t="str">
         <x:v>3790610</x:v>
       </x:c>
       <x:c r="T345" s="10" t="str">
@@ -21756,7 +21828,7 @@
       <x:c r="R346" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S346" s="9" t="n">
+      <x:c r="S346" s="9" t="str">
         <x:v>4528510</x:v>
       </x:c>
       <x:c r="T346" s="10" t="str">
@@ -21817,7 +21889,7 @@
       <x:c r="R347" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S347" s="9" t="n">
+      <x:c r="S347" s="9" t="str">
         <x:v>4528519</x:v>
       </x:c>
       <x:c r="T347" s="10" t="str">
@@ -21880,7 +21952,7 @@
       <x:c r="R348" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S348" s="9" t="n">
+      <x:c r="S348" s="9" t="str">
         <x:v>4528668</x:v>
       </x:c>
       <x:c r="T348" s="10" t="str">
@@ -21941,7 +22013,7 @@
       <x:c r="R349" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S349" s="9" t="n">
+      <x:c r="S349" s="9" t="str">
         <x:v>4528780</x:v>
       </x:c>
       <x:c r="T349" s="10" t="str">
@@ -22002,7 +22074,7 @@
       <x:c r="R350" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S350" s="9" t="n">
+      <x:c r="S350" s="9" t="str">
         <x:v>4814276</x:v>
       </x:c>
       <x:c r="T350" s="10" t="str">
@@ -22063,7 +22135,7 @@
       <x:c r="R351" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S351" s="9" t="n">
+      <x:c r="S351" s="9" t="str">
         <x:v>4814468</x:v>
       </x:c>
       <x:c r="T351" s="10" t="str">
@@ -22124,7 +22196,7 @@
       <x:c r="R352" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S352" s="9" t="n">
+      <x:c r="S352" s="9" t="str">
         <x:v>4814492</x:v>
       </x:c>
       <x:c r="T352" s="10" t="str">
@@ -22185,7 +22257,7 @@
       <x:c r="R353" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S353" s="9" t="n">
+      <x:c r="S353" s="9" t="str">
         <x:v>4814518</x:v>
       </x:c>
       <x:c r="T353" s="10" t="str">
@@ -22246,7 +22318,7 @@
       <x:c r="R354" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S354" s="9" t="n">
+      <x:c r="S354" s="9" t="str">
         <x:v>4814521</x:v>
       </x:c>
       <x:c r="T354" s="10" t="str">
@@ -22307,7 +22379,7 @@
       <x:c r="R355" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S355" s="9" t="n">
+      <x:c r="S355" s="9" t="str">
         <x:v>4814864</x:v>
       </x:c>
       <x:c r="T355" s="10" t="str">
@@ -22368,7 +22440,7 @@
       <x:c r="R356" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S356" s="9" t="n">
+      <x:c r="S356" s="9" t="str">
         <x:v>4814866</x:v>
       </x:c>
       <x:c r="T356" s="10" t="str">
@@ -22429,7 +22501,7 @@
       <x:c r="R357" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S357" s="9" t="n">
+      <x:c r="S357" s="9" t="str">
         <x:v>4814876</x:v>
       </x:c>
       <x:c r="T357" s="10" t="str">
@@ -22490,7 +22562,7 @@
       <x:c r="R358" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S358" s="9" t="n">
+      <x:c r="S358" s="9" t="str">
         <x:v>4814964</x:v>
       </x:c>
       <x:c r="T358" s="10" t="str">
@@ -22551,7 +22623,7 @@
       <x:c r="R359" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S359" s="9" t="n">
+      <x:c r="S359" s="9" t="str">
         <x:v>6900398</x:v>
       </x:c>
       <x:c r="T359" s="10" t="str">
@@ -22612,7 +22684,7 @@
       <x:c r="R360" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S360" s="9" t="n">
+      <x:c r="S360" s="9" t="str">
         <x:v>6900399</x:v>
       </x:c>
       <x:c r="T360" s="10" t="str">
@@ -22667,7 +22739,7 @@
       <x:c r="R361" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S361" s="9" t="n">
+      <x:c r="S361" s="9" t="str">
         <x:v>3741878</x:v>
       </x:c>
       <x:c r="T361" s="10" t="str">
@@ -22722,7 +22794,7 @@
       <x:c r="R362" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S362" s="9" t="n">
+      <x:c r="S362" s="9" t="str">
         <x:v>3742178</x:v>
       </x:c>
       <x:c r="T362" s="10" t="str">
@@ -22777,7 +22849,7 @@
       <x:c r="R363" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S363" s="9" t="n">
+      <x:c r="S363" s="9" t="str">
         <x:v>3742190</x:v>
       </x:c>
       <x:c r="T363" s="10" t="str">
@@ -22832,7 +22904,7 @@
       <x:c r="R364" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S364" s="9" t="n">
+      <x:c r="S364" s="9" t="str">
         <x:v>5087849</x:v>
       </x:c>
       <x:c r="T364" s="10" t="str">
@@ -22887,7 +22959,7 @@
       <x:c r="R365" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S365" s="9" t="n">
+      <x:c r="S365" s="9" t="str">
         <x:v>5087853</x:v>
       </x:c>
       <x:c r="T365" s="10" t="str">
@@ -22942,7 +23014,7 @@
       <x:c r="R366" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S366" s="9" t="n">
+      <x:c r="S366" s="9" t="str">
         <x:v>5087855</x:v>
       </x:c>
       <x:c r="T366" s="10" t="str">
@@ -23000,7 +23072,7 @@
       <x:c r="R367" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S367" s="9" t="n">
+      <x:c r="S367" s="9" t="str">
         <x:v>5087856</x:v>
       </x:c>
       <x:c r="T367" s="10" t="str">
@@ -23064,7 +23136,7 @@
       <x:c r="R368" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S368" s="9" t="n">
+      <x:c r="S368" s="9" t="str">
         <x:v>3731182</x:v>
       </x:c>
       <x:c r="T368" s="10" t="str">
@@ -23128,7 +23200,7 @@
       <x:c r="R369" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S369" s="9" t="n">
+      <x:c r="S369" s="9" t="str">
         <x:v>3731582</x:v>
       </x:c>
       <x:c r="T369" s="10" t="str">
@@ -23192,7 +23264,7 @@
       <x:c r="R370" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S370" s="9" t="n">
+      <x:c r="S370" s="9" t="str">
         <x:v>3741825</x:v>
       </x:c>
       <x:c r="T370" s="10" t="str">
@@ -23256,7 +23328,7 @@
       <x:c r="R371" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S371" s="9" t="n">
+      <x:c r="S371" s="9" t="str">
         <x:v>3742133</x:v>
       </x:c>
       <x:c r="T371" s="10" t="str">
@@ -23320,7 +23392,7 @@
       <x:c r="R372" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S372" s="9" t="n">
+      <x:c r="S372" s="9" t="str">
         <x:v>4324629</x:v>
       </x:c>
       <x:c r="T372" s="10" t="str">
@@ -23384,7 +23456,7 @@
       <x:c r="R373" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S373" s="9" t="n">
+      <x:c r="S373" s="9" t="str">
         <x:v>4324630</x:v>
       </x:c>
       <x:c r="T373" s="10" t="str">
@@ -23448,7 +23520,7 @@
       <x:c r="R374" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S374" s="9" t="n">
+      <x:c r="S374" s="9" t="str">
         <x:v>4324633</x:v>
       </x:c>
       <x:c r="T374" s="10" t="str">
@@ -23512,7 +23584,7 @@
       <x:c r="R375" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S375" s="9" t="n">
+      <x:c r="S375" s="9" t="str">
         <x:v>4330194</x:v>
       </x:c>
       <x:c r="T375" s="10" t="str">
@@ -23576,7 +23648,7 @@
       <x:c r="R376" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S376" s="9" t="n">
+      <x:c r="S376" s="9" t="str">
         <x:v>4330195</x:v>
       </x:c>
       <x:c r="T376" s="10" t="str">
@@ -23640,7 +23712,7 @@
       <x:c r="R377" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S377" s="9" t="n">
+      <x:c r="S377" s="9" t="str">
         <x:v>5087838</x:v>
       </x:c>
       <x:c r="T377" s="10" t="str">
@@ -23704,7 +23776,7 @@
       <x:c r="R378" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S378" s="9" t="n">
+      <x:c r="S378" s="9" t="str">
         <x:v>5087839</x:v>
       </x:c>
       <x:c r="T378" s="10" t="str">
@@ -23768,7 +23840,7 @@
       <x:c r="R379" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S379" s="9" t="n">
+      <x:c r="S379" s="9" t="str">
         <x:v>4330479</x:v>
       </x:c>
       <x:c r="T379" s="10" t="str">
@@ -23832,7 +23904,7 @@
       <x:c r="R380" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S380" s="9" t="n">
+      <x:c r="S380" s="9" t="str">
         <x:v>3787832</x:v>
       </x:c>
       <x:c r="T380" s="10" t="str">
@@ -23896,7 +23968,7 @@
       <x:c r="R381" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S381" s="9" t="n">
+      <x:c r="S381" s="9" t="str">
         <x:v>3787861</x:v>
       </x:c>
       <x:c r="T381" s="10" t="str">
@@ -23960,7 +24032,7 @@
       <x:c r="R382" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S382" s="9" t="n">
+      <x:c r="S382" s="9" t="str">
         <x:v>3790597</x:v>
       </x:c>
       <x:c r="T382" s="10" t="str">
@@ -24024,7 +24096,7 @@
       <x:c r="R383" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S383" s="9" t="n">
+      <x:c r="S383" s="9" t="str">
         <x:v>3790806</x:v>
       </x:c>
       <x:c r="T383" s="10" t="str">
@@ -24088,7 +24160,7 @@
       <x:c r="R384" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S384" s="9" t="n">
+      <x:c r="S384" s="9" t="str">
         <x:v>3790807</x:v>
       </x:c>
       <x:c r="T384" s="10" t="str">
@@ -24152,7 +24224,7 @@
       <x:c r="R385" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S385" s="9" t="n">
+      <x:c r="S385" s="9" t="str">
         <x:v>3790839</x:v>
       </x:c>
       <x:c r="T385" s="10" t="str">
@@ -24216,7 +24288,7 @@
       <x:c r="R386" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S386" s="9" t="n">
+      <x:c r="S386" s="9" t="str">
         <x:v>3791070</x:v>
       </x:c>
       <x:c r="T386" s="10" t="str">
@@ -24280,7 +24352,7 @@
       <x:c r="R387" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S387" s="9" t="n">
+      <x:c r="S387" s="9" t="str">
         <x:v>4528894</x:v>
       </x:c>
       <x:c r="T387" s="10" t="str">
@@ -24344,7 +24416,7 @@
       <x:c r="R388" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S388" s="9" t="n">
+      <x:c r="S388" s="9" t="str">
         <x:v>4814363</x:v>
       </x:c>
       <x:c r="T388" s="10" t="str">
@@ -24408,7 +24480,7 @@
       <x:c r="R389" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S389" s="9" t="n">
+      <x:c r="S389" s="9" t="str">
         <x:v>4814611</x:v>
       </x:c>
       <x:c r="T389" s="10" t="str">
@@ -24472,7 +24544,7 @@
       <x:c r="R390" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S390" s="9" t="n">
+      <x:c r="S390" s="9" t="str">
         <x:v>5087850</x:v>
       </x:c>
       <x:c r="T390" s="10" t="str">
@@ -24536,7 +24608,7 @@
       <x:c r="R391" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S391" s="9" t="n">
+      <x:c r="S391" s="9" t="str">
         <x:v>5087851</x:v>
       </x:c>
       <x:c r="T391" s="10" t="str">
@@ -24600,7 +24672,7 @@
       <x:c r="R392" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S392" s="9" t="n">
+      <x:c r="S392" s="9" t="str">
         <x:v>5087854</x:v>
       </x:c>
       <x:c r="T392" s="10" t="str">
@@ -24664,7 +24736,7 @@
       <x:c r="R393" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S393" s="9" t="n">
+      <x:c r="S393" s="9" t="str">
         <x:v>6900396</x:v>
       </x:c>
       <x:c r="T393" s="10" t="str">
@@ -24728,7 +24800,7 @@
       <x:c r="R394" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S394" s="9" t="n">
+      <x:c r="S394" s="9" t="str">
         <x:v>6900397</x:v>
       </x:c>
       <x:c r="T394" s="10" t="str">
@@ -24783,7 +24855,7 @@
       <x:c r="R395" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S395" s="9" t="n">
+      <x:c r="S395" s="9" t="str">
         <x:v>4330229</x:v>
       </x:c>
       <x:c r="T395" s="10" t="str">
@@ -24838,7 +24910,7 @@
       <x:c r="R396" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S396" s="9" t="n">
+      <x:c r="S396" s="9" t="str">
         <x:v>4330376</x:v>
       </x:c>
       <x:c r="T396" s="10" t="str">
@@ -24893,7 +24965,7 @@
       <x:c r="R397" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S397" s="9" t="n">
+      <x:c r="S397" s="9" t="str">
         <x:v>6900402</x:v>
       </x:c>
       <x:c r="T397" s="10" t="str">
@@ -24948,7 +25020,7 @@
       <x:c r="R398" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S398" s="9" t="n">
+      <x:c r="S398" s="9" t="str">
         <x:v>6900400</x:v>
       </x:c>
       <x:c r="T398" s="10" t="str">
@@ -25003,7 +25075,7 @@
       <x:c r="R399" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S399" s="9" t="n">
+      <x:c r="S399" s="9" t="str">
         <x:v>4814432</x:v>
       </x:c>
       <x:c r="T399" s="10" t="str">
@@ -25058,7 +25130,7 @@
       <x:c r="R400" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S400" s="9" t="n">
+      <x:c r="S400" s="9" t="str">
         <x:v>4814438</x:v>
       </x:c>
       <x:c r="T400" s="10" t="str">
@@ -25113,7 +25185,7 @@
       <x:c r="R401" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S401" s="9" t="n">
+      <x:c r="S401" s="9" t="str">
         <x:v>4814441</x:v>
       </x:c>
       <x:c r="T401" s="10" t="str">
@@ -25168,7 +25240,7 @@
       <x:c r="R402" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S402" s="9" t="n">
+      <x:c r="S402" s="9" t="str">
         <x:v>4814958</x:v>
       </x:c>
       <x:c r="T402" s="10" t="str">
@@ -25229,7 +25301,7 @@
       <x:c r="R403" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S403" s="9" t="n">
+      <x:c r="S403" s="9" t="str">
         <x:v>3741053</x:v>
       </x:c>
       <x:c r="T403" s="10" t="str">
@@ -25290,7 +25362,7 @@
       <x:c r="R404" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S404" s="9" t="n">
+      <x:c r="S404" s="9" t="str">
         <x:v>3741688</x:v>
       </x:c>
       <x:c r="T404" s="10" t="str">
@@ -25351,7 +25423,7 @@
       <x:c r="R405" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S405" s="9" t="n">
+      <x:c r="S405" s="9" t="str">
         <x:v>4330145</x:v>
       </x:c>
       <x:c r="T405" s="10" t="str">
@@ -25412,7 +25484,7 @@
       <x:c r="R406" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S406" s="9" t="n">
+      <x:c r="S406" s="9" t="str">
         <x:v>4330172</x:v>
       </x:c>
       <x:c r="T406" s="10" t="str">
@@ -25473,7 +25545,7 @@
       <x:c r="R407" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S407" s="9" t="n">
+      <x:c r="S407" s="9" t="str">
         <x:v>4330287</x:v>
       </x:c>
       <x:c r="T407" s="10" t="str">
@@ -25534,7 +25606,7 @@
       <x:c r="R408" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S408" s="9" t="n">
+      <x:c r="S408" s="9" t="str">
         <x:v>4324639</x:v>
       </x:c>
       <x:c r="T408" s="10" t="str">
@@ -25595,7 +25667,7 @@
       <x:c r="R409" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S409" s="9" t="n">
+      <x:c r="S409" s="9" t="str">
         <x:v>4330290</x:v>
       </x:c>
       <x:c r="T409" s="10" t="str">
@@ -25656,7 +25728,7 @@
       <x:c r="R410" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S410" s="9" t="n">
+      <x:c r="S410" s="9" t="str">
         <x:v>3787775</x:v>
       </x:c>
       <x:c r="T410" s="10" t="str">
@@ -25717,7 +25789,7 @@
       <x:c r="R411" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S411" s="9" t="n">
+      <x:c r="S411" s="9" t="str">
         <x:v>3789748</x:v>
       </x:c>
       <x:c r="T411" s="10" t="str">
@@ -25778,7 +25850,7 @@
       <x:c r="R412" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S412" s="9" t="n">
+      <x:c r="S412" s="9" t="str">
         <x:v>3789874</x:v>
       </x:c>
       <x:c r="T412" s="10" t="str">
@@ -25839,7 +25911,7 @@
       <x:c r="R413" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S413" s="9" t="n">
+      <x:c r="S413" s="9" t="str">
         <x:v>3790755</x:v>
       </x:c>
       <x:c r="T413" s="10" t="str">
@@ -25904,7 +25976,7 @@
       <x:c r="R414" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S414" s="9" t="n">
+      <x:c r="S414" s="9" t="str">
         <x:v>4529106</x:v>
       </x:c>
       <x:c r="T414" s="10" t="str">
@@ -25965,7 +26037,7 @@
       <x:c r="R415" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S415" s="9" t="n">
+      <x:c r="S415" s="9" t="str">
         <x:v>4814510</x:v>
       </x:c>
       <x:c r="T415" s="10" t="str">
@@ -26026,7 +26098,7 @@
       <x:c r="R416" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S416" s="9" t="n">
+      <x:c r="S416" s="9" t="str">
         <x:v>4814537</x:v>
       </x:c>
       <x:c r="T416" s="10" t="str">
@@ -26087,7 +26159,7 @@
       <x:c r="R417" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S417" s="9" t="n">
+      <x:c r="S417" s="9" t="str">
         <x:v>4815031</x:v>
       </x:c>
       <x:c r="T417" s="10" t="str">
@@ -26148,7 +26220,7 @@
       <x:c r="R418" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S418" s="9" t="n">
+      <x:c r="S418" s="9" t="str">
         <x:v>5099007</x:v>
       </x:c>
       <x:c r="T418" s="10" t="str">
@@ -26212,7 +26284,7 @@
       <x:c r="R419" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S419" s="9" t="n">
+      <x:c r="S419" s="9" t="str">
         <x:v>3731570</x:v>
       </x:c>
       <x:c r="T419" s="10" t="str">
@@ -26276,7 +26348,7 @@
       <x:c r="R420" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S420" s="9" t="n">
+      <x:c r="S420" s="9" t="str">
         <x:v>3742123</x:v>
       </x:c>
       <x:c r="T420" s="10" t="str">
@@ -26340,7 +26412,7 @@
       <x:c r="R421" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S421" s="9" t="n">
+      <x:c r="S421" s="9" t="str">
         <x:v>4324455</x:v>
       </x:c>
       <x:c r="T421" s="10" t="str">
@@ -26404,7 +26476,7 @@
       <x:c r="R422" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S422" s="9" t="n">
+      <x:c r="S422" s="9" t="str">
         <x:v>4330197</x:v>
       </x:c>
       <x:c r="T422" s="10" t="str">
@@ -26468,7 +26540,7 @@
       <x:c r="R423" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S423" s="9" t="n">
+      <x:c r="S423" s="9" t="str">
         <x:v>4330338</x:v>
       </x:c>
       <x:c r="T423" s="10" t="str">
@@ -26533,7 +26605,7 @@
       <x:c r="R424" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S424" s="9" t="n">
+      <x:c r="S424" s="9" t="str">
         <x:v>3731186</x:v>
       </x:c>
       <x:c r="T424" s="10" t="str">
@@ -26597,7 +26669,7 @@
       <x:c r="R425" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S425" s="9" t="n">
+      <x:c r="S425" s="9" t="str">
         <x:v>4324645</x:v>
       </x:c>
       <x:c r="T425" s="10" t="str">
@@ -26661,7 +26733,7 @@
       <x:c r="R426" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S426" s="9" t="n">
+      <x:c r="S426" s="9" t="str">
         <x:v>3790608</x:v>
       </x:c>
       <x:c r="T426" s="10" t="str">
@@ -26731,7 +26803,7 @@
       <x:c r="R427" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S427" s="9" t="n">
+      <x:c r="S427" s="9" t="str">
         <x:v>4528697</x:v>
       </x:c>
       <x:c r="T427" s="10" t="str">
@@ -26795,7 +26867,7 @@
       <x:c r="R428" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S428" s="9" t="n">
+      <x:c r="S428" s="9" t="str">
         <x:v>4528885</x:v>
       </x:c>
       <x:c r="T428" s="10" t="str">
@@ -26859,7 +26931,7 @@
       <x:c r="R429" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S429" s="9" t="n">
+      <x:c r="S429" s="9" t="str">
         <x:v>4529165</x:v>
       </x:c>
       <x:c r="T429" s="10" t="str">
@@ -26923,7 +26995,7 @@
       <x:c r="R430" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S430" s="9" t="n">
+      <x:c r="S430" s="9" t="str">
         <x:v>4814615</x:v>
       </x:c>
       <x:c r="T430" s="10" t="str">
@@ -26987,7 +27059,7 @@
       <x:c r="R431" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S431" s="9" t="n">
+      <x:c r="S431" s="9" t="str">
         <x:v>5099006</x:v>
       </x:c>
       <x:c r="T431" s="10" t="str">
@@ -27042,7 +27114,7 @@
       <x:c r="R432" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S432" s="9" t="n">
+      <x:c r="S432" s="9" t="str">
         <x:v>4324650</x:v>
       </x:c>
       <x:c r="T432" s="10" t="str">
@@ -27097,7 +27169,7 @@
       <x:c r="R433" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S433" s="9" t="n">
+      <x:c r="S433" s="9" t="str">
         <x:v>4324651</x:v>
       </x:c>
       <x:c r="T433" s="10" t="str">
@@ -27152,7 +27224,7 @@
       <x:c r="R434" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S434" s="9" t="n">
+      <x:c r="S434" s="9" t="str">
         <x:v>4324649</x:v>
       </x:c>
       <x:c r="T434" s="10" t="str">
@@ -27219,7 +27291,7 @@
       <x:c r="R435" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S435" s="9" t="n">
+      <x:c r="S435" s="9" t="str">
         <x:v>3741417</x:v>
       </x:c>
       <x:c r="T435" s="10" t="str">
@@ -27280,7 +27352,7 @@
       <x:c r="R436" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S436" s="9" t="n">
+      <x:c r="S436" s="9" t="str">
         <x:v>3742047</x:v>
       </x:c>
       <x:c r="T436" s="10" t="str">
@@ -27350,7 +27422,7 @@
       <x:c r="R437" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S437" s="9" t="n">
+      <x:c r="S437" s="9" t="str">
         <x:v>3742048</x:v>
       </x:c>
       <x:c r="T437" s="10" t="str">
@@ -27411,7 +27483,7 @@
       <x:c r="R438" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S438" s="9" t="n">
+      <x:c r="S438" s="9" t="str">
         <x:v>4324657</x:v>
       </x:c>
       <x:c r="T438" s="10" t="str">
@@ -27472,7 +27544,7 @@
       <x:c r="R439" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S439" s="9" t="n">
+      <x:c r="S439" s="9" t="str">
         <x:v>4324660</x:v>
       </x:c>
       <x:c r="T439" s="10" t="str">
@@ -27533,7 +27605,7 @@
       <x:c r="R440" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S440" s="9" t="n">
+      <x:c r="S440" s="9" t="str">
         <x:v>4330148</x:v>
       </x:c>
       <x:c r="T440" s="10" t="str">
@@ -27594,7 +27666,7 @@
       <x:c r="R441" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S441" s="9" t="n">
+      <x:c r="S441" s="9" t="str">
         <x:v>4330152</x:v>
       </x:c>
       <x:c r="T441" s="10" t="str">
@@ -27655,7 +27727,7 @@
       <x:c r="R442" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S442" s="9" t="n">
+      <x:c r="S442" s="9" t="str">
         <x:v>4330174</x:v>
       </x:c>
       <x:c r="T442" s="10" t="str">
@@ -27716,7 +27788,7 @@
       <x:c r="R443" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S443" s="9" t="n">
+      <x:c r="S443" s="9" t="str">
         <x:v>4330294</x:v>
       </x:c>
       <x:c r="T443" s="10" t="str">
@@ -27777,7 +27849,7 @@
       <x:c r="R444" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S444" s="9" t="n">
+      <x:c r="S444" s="9" t="str">
         <x:v>4330296</x:v>
       </x:c>
       <x:c r="T444" s="10" t="str">
@@ -27838,7 +27910,7 @@
       <x:c r="R445" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S445" s="9" t="n">
+      <x:c r="S445" s="9" t="str">
         <x:v>4330298</x:v>
       </x:c>
       <x:c r="T445" s="10" t="str">
@@ -27899,7 +27971,7 @@
       <x:c r="R446" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S446" s="9" t="n">
+      <x:c r="S446" s="9" t="str">
         <x:v>4330434</x:v>
       </x:c>
       <x:c r="T446" s="10" t="str">
@@ -27960,7 +28032,7 @@
       <x:c r="R447" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S447" s="9" t="n">
+      <x:c r="S447" s="9" t="str">
         <x:v>4330435</x:v>
       </x:c>
       <x:c r="T447" s="10" t="str">
@@ -28021,7 +28093,7 @@
       <x:c r="R448" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S448" s="9" t="n">
+      <x:c r="S448" s="9" t="str">
         <x:v>4330438</x:v>
       </x:c>
       <x:c r="T448" s="10" t="str">
@@ -28086,7 +28158,7 @@
       <x:c r="R449" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S449" s="9" t="n">
+      <x:c r="S449" s="9" t="str">
         <x:v>4529128</x:v>
       </x:c>
       <x:c r="T449" s="10" t="str">
@@ -28147,7 +28219,7 @@
       <x:c r="R450" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S450" s="9" t="n">
+      <x:c r="S450" s="9" t="str">
         <x:v>4814702</x:v>
       </x:c>
       <x:c r="T450" s="10" t="str">
@@ -28208,7 +28280,7 @@
       <x:c r="R451" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S451" s="9" t="n">
+      <x:c r="S451" s="9" t="str">
         <x:v>5155235</x:v>
       </x:c>
       <x:c r="T451" s="10" t="str">
@@ -28269,7 +28341,7 @@
       <x:c r="R452" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S452" s="9" t="n">
+      <x:c r="S452" s="9" t="str">
         <x:v>4324655</x:v>
       </x:c>
       <x:c r="T452" s="10" t="str">
@@ -28330,7 +28402,7 @@
       <x:c r="R453" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S453" s="9" t="n">
+      <x:c r="S453" s="9" t="str">
         <x:v>4330149</x:v>
       </x:c>
       <x:c r="T453" s="10" t="str">
@@ -28391,7 +28463,7 @@
       <x:c r="R454" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S454" s="9" t="n">
+      <x:c r="S454" s="9" t="str">
         <x:v>4330175</x:v>
       </x:c>
       <x:c r="T454" s="10" t="str">
@@ -28452,7 +28524,7 @@
       <x:c r="R455" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S455" s="9" t="n">
+      <x:c r="S455" s="9" t="str">
         <x:v>4330436</x:v>
       </x:c>
       <x:c r="T455" s="10" t="str">
@@ -28513,7 +28585,7 @@
       <x:c r="R456" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S456" s="9" t="n">
+      <x:c r="S456" s="9" t="str">
         <x:v>3769035</x:v>
       </x:c>
       <x:c r="T456" s="10" t="str">
@@ -28574,7 +28646,7 @@
       <x:c r="R457" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S457" s="9" t="n">
+      <x:c r="S457" s="9" t="str">
         <x:v>3786140</x:v>
       </x:c>
       <x:c r="T457" s="10" t="str">
@@ -28635,7 +28707,7 @@
       <x:c r="R458" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S458" s="9" t="n">
+      <x:c r="S458" s="9" t="str">
         <x:v>3787716</x:v>
       </x:c>
       <x:c r="T458" s="10" t="str">
@@ -28696,7 +28768,7 @@
       <x:c r="R459" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S459" s="9" t="n">
+      <x:c r="S459" s="9" t="str">
         <x:v>3787730</x:v>
       </x:c>
       <x:c r="T459" s="10" t="str">
@@ -28757,7 +28829,7 @@
       <x:c r="R460" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S460" s="9" t="n">
+      <x:c r="S460" s="9" t="str">
         <x:v>3787783</x:v>
       </x:c>
       <x:c r="T460" s="10" t="str">
@@ -28818,7 +28890,7 @@
       <x:c r="R461" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S461" s="9" t="n">
+      <x:c r="S461" s="9" t="str">
         <x:v>3789752</x:v>
       </x:c>
       <x:c r="T461" s="10" t="str">
@@ -28879,7 +28951,7 @@
       <x:c r="R462" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S462" s="9" t="n">
+      <x:c r="S462" s="9" t="str">
         <x:v>3790322</x:v>
       </x:c>
       <x:c r="T462" s="10" t="str">
@@ -28940,7 +29012,7 @@
       <x:c r="R463" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S463" s="9" t="n">
+      <x:c r="S463" s="9" t="str">
         <x:v>3790689</x:v>
       </x:c>
       <x:c r="T463" s="10" t="str">
@@ -29001,7 +29073,7 @@
       <x:c r="R464" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S464" s="9" t="n">
+      <x:c r="S464" s="9" t="str">
         <x:v>4528617</x:v>
       </x:c>
       <x:c r="T464" s="10" t="str">
@@ -29062,7 +29134,7 @@
       <x:c r="R465" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S465" s="9" t="n">
+      <x:c r="S465" s="9" t="str">
         <x:v>4814310</x:v>
       </x:c>
       <x:c r="T465" s="10" t="str">
@@ -29123,7 +29195,7 @@
       <x:c r="R466" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S466" s="9" t="n">
+      <x:c r="S466" s="9" t="str">
         <x:v>4814845</x:v>
       </x:c>
       <x:c r="T466" s="10" t="str">
@@ -29184,7 +29256,7 @@
       <x:c r="R467" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S467" s="9" t="n">
+      <x:c r="S467" s="9" t="str">
         <x:v>4814878</x:v>
       </x:c>
       <x:c r="T467" s="10" t="str">
@@ -29245,7 +29317,7 @@
       <x:c r="R468" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S468" s="9" t="n">
+      <x:c r="S468" s="9" t="str">
         <x:v>4814885</x:v>
       </x:c>
       <x:c r="T468" s="10" t="str">
@@ -29306,7 +29378,7 @@
       <x:c r="R469" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S469" s="9" t="n">
+      <x:c r="S469" s="9" t="str">
         <x:v>4814996</x:v>
       </x:c>
       <x:c r="T469" s="10" t="str">
@@ -29375,7 +29447,7 @@
       <x:c r="R470" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S470" s="9" t="n">
+      <x:c r="S470" s="9" t="str">
         <x:v>3731205</x:v>
       </x:c>
       <x:c r="T470" s="10" t="str">
@@ -29439,7 +29511,7 @@
       <x:c r="R471" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S471" s="9" t="n">
+      <x:c r="S471" s="9" t="str">
         <x:v>3741783</x:v>
       </x:c>
       <x:c r="T471" s="10" t="str">
@@ -29503,7 +29575,7 @@
       <x:c r="R472" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S472" s="9" t="n">
+      <x:c r="S472" s="9" t="str">
         <x:v>4324661</x:v>
       </x:c>
       <x:c r="T472" s="10" t="str">
@@ -29567,7 +29639,7 @@
       <x:c r="R473" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S473" s="9" t="n">
+      <x:c r="S473" s="9" t="str">
         <x:v>4324662</x:v>
       </x:c>
       <x:c r="T473" s="10" t="str">
@@ -29631,7 +29703,7 @@
       <x:c r="R474" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S474" s="9" t="n">
+      <x:c r="S474" s="9" t="str">
         <x:v>4324663</x:v>
       </x:c>
       <x:c r="T474" s="10" t="str">
@@ -29695,7 +29767,7 @@
       <x:c r="R475" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S475" s="9" t="n">
+      <x:c r="S475" s="9" t="str">
         <x:v>4324666</x:v>
       </x:c>
       <x:c r="T475" s="10" t="str">
@@ -29759,7 +29831,7 @@
       <x:c r="R476" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S476" s="9" t="n">
+      <x:c r="S476" s="9" t="str">
         <x:v>4324667</x:v>
       </x:c>
       <x:c r="T476" s="10" t="str">
@@ -29823,7 +29895,7 @@
       <x:c r="R477" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S477" s="9" t="n">
+      <x:c r="S477" s="9" t="str">
         <x:v>4330200</x:v>
       </x:c>
       <x:c r="T477" s="10" t="str">
@@ -29887,7 +29959,7 @@
       <x:c r="R478" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S478" s="9" t="n">
+      <x:c r="S478" s="9" t="str">
         <x:v>4330341</x:v>
       </x:c>
       <x:c r="T478" s="10" t="str">
@@ -29951,7 +30023,7 @@
       <x:c r="R479" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S479" s="9" t="n">
+      <x:c r="S479" s="9" t="str">
         <x:v>4330483</x:v>
       </x:c>
       <x:c r="T479" s="10" t="str">
@@ -30015,7 +30087,7 @@
       <x:c r="R480" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S480" s="9" t="n">
+      <x:c r="S480" s="9" t="str">
         <x:v>4330485</x:v>
       </x:c>
       <x:c r="T480" s="10" t="str">
@@ -30079,7 +30151,7 @@
       <x:c r="R481" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S481" s="9" t="n">
+      <x:c r="S481" s="9" t="str">
         <x:v>4528706</x:v>
       </x:c>
       <x:c r="T481" s="10" t="str">
@@ -30143,7 +30215,7 @@
       <x:c r="R482" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S482" s="9" t="n">
+      <x:c r="S482" s="9" t="str">
         <x:v>5155299</x:v>
       </x:c>
       <x:c r="T482" s="10" t="str">
@@ -30207,7 +30279,7 @@
       <x:c r="R483" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S483" s="9" t="n">
+      <x:c r="S483" s="9" t="str">
         <x:v>3790619</x:v>
       </x:c>
       <x:c r="T483" s="10" t="str">
@@ -30271,7 +30343,7 @@
       <x:c r="R484" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S484" s="9" t="n">
+      <x:c r="S484" s="9" t="str">
         <x:v>3790810</x:v>
       </x:c>
       <x:c r="T484" s="10" t="str">
@@ -30342,7 +30414,7 @@
       <x:c r="R485" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S485" s="9" t="n">
+      <x:c r="S485" s="9" t="str">
         <x:v>4528888</x:v>
       </x:c>
       <x:c r="T485" s="10" t="str">
@@ -30406,7 +30478,7 @@
       <x:c r="R486" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S486" s="9" t="n">
+      <x:c r="S486" s="9" t="str">
         <x:v>4814368</x:v>
       </x:c>
       <x:c r="T486" s="10" t="str">
@@ -30470,7 +30542,7 @@
       <x:c r="R487" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S487" s="9" t="n">
+      <x:c r="S487" s="9" t="str">
         <x:v>4814372</x:v>
       </x:c>
       <x:c r="T487" s="10" t="str">
@@ -30534,7 +30606,7 @@
       <x:c r="R488" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S488" s="9" t="n">
+      <x:c r="S488" s="9" t="str">
         <x:v>4814374</x:v>
       </x:c>
       <x:c r="T488" s="10" t="str">
@@ -30598,7 +30670,7 @@
       <x:c r="R489" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S489" s="9" t="n">
+      <x:c r="S489" s="9" t="str">
         <x:v>4814614</x:v>
       </x:c>
       <x:c r="T489" s="10" t="str">
@@ -30662,7 +30734,7 @@
       <x:c r="R490" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S490" s="9" t="n">
+      <x:c r="S490" s="9" t="str">
         <x:v>4814937</x:v>
       </x:c>
       <x:c r="T490" s="10" t="str">
@@ -30726,7 +30798,7 @@
       <x:c r="R491" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S491" s="9" t="n">
+      <x:c r="S491" s="9" t="str">
         <x:v>4815070</x:v>
       </x:c>
       <x:c r="T491" s="10" t="str">
@@ -30781,7 +30853,7 @@
       <x:c r="R492" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S492" s="9" t="n">
+      <x:c r="S492" s="9" t="str">
         <x:v>4324670</x:v>
       </x:c>
       <x:c r="T492" s="10" t="str">
@@ -30836,7 +30908,7 @@
       <x:c r="R493" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S493" s="9" t="n">
+      <x:c r="S493" s="9" t="str">
         <x:v>4324671</x:v>
       </x:c>
       <x:c r="T493" s="10" t="str">
@@ -30891,7 +30963,7 @@
       <x:c r="R494" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S494" s="9" t="n">
+      <x:c r="S494" s="9" t="str">
         <x:v>4324672</x:v>
       </x:c>
       <x:c r="T494" s="10" t="str">
@@ -30946,7 +31018,7 @@
       <x:c r="R495" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S495" s="9" t="n">
+      <x:c r="S495" s="9" t="str">
         <x:v>4814642</x:v>
       </x:c>
       <x:c r="T495" s="10" t="str">
@@ -31007,7 +31079,7 @@
       <x:c r="R496" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S496" s="9" t="n">
+      <x:c r="S496" s="9" t="str">
         <x:v>3731109</x:v>
       </x:c>
       <x:c r="T496" s="10" t="str">
@@ -31068,7 +31140,7 @@
       <x:c r="R497" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S497" s="9" t="n">
+      <x:c r="S497" s="9" t="str">
         <x:v>3731464</x:v>
       </x:c>
       <x:c r="T497" s="10" t="str">
@@ -31129,7 +31201,7 @@
       <x:c r="R498" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S498" s="9" t="n">
+      <x:c r="S498" s="9" t="str">
         <x:v>3741684</x:v>
       </x:c>
       <x:c r="T498" s="10" t="str">
@@ -31193,7 +31265,7 @@
       <x:c r="R499" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S499" s="9" t="n">
+      <x:c r="S499" s="9" t="str">
         <x:v>3741693</x:v>
       </x:c>
       <x:c r="T499" s="10" t="str">
@@ -31254,7 +31326,7 @@
       <x:c r="R500" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S500" s="9" t="n">
+      <x:c r="S500" s="9" t="str">
         <x:v>4324440</x:v>
       </x:c>
       <x:c r="T500" s="10" t="str">
@@ -31315,7 +31387,7 @@
       <x:c r="R501" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S501" s="9" t="n">
+      <x:c r="S501" s="9" t="str">
         <x:v>4324622</x:v>
       </x:c>
       <x:c r="T501" s="10" t="str">
@@ -31376,7 +31448,7 @@
       <x:c r="R502" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S502" s="9" t="n">
+      <x:c r="S502" s="9" t="str">
         <x:v>4324673</x:v>
       </x:c>
       <x:c r="T502" s="10" t="str">
@@ -31437,7 +31509,7 @@
       <x:c r="R503" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S503" s="9" t="n">
+      <x:c r="S503" s="9" t="str">
         <x:v>4324675</x:v>
       </x:c>
       <x:c r="T503" s="10" t="str">
@@ -31498,7 +31570,7 @@
       <x:c r="R504" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S504" s="9" t="n">
+      <x:c r="S504" s="9" t="str">
         <x:v>4330156</x:v>
       </x:c>
       <x:c r="T504" s="10" t="str">
@@ -31559,7 +31631,7 @@
       <x:c r="R505" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S505" s="9" t="n">
+      <x:c r="S505" s="9" t="str">
         <x:v>4330300</x:v>
       </x:c>
       <x:c r="T505" s="10" t="str">
@@ -31620,7 +31692,7 @@
       <x:c r="R506" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S506" s="9" t="n">
+      <x:c r="S506" s="9" t="str">
         <x:v>4330304</x:v>
       </x:c>
       <x:c r="T506" s="10" t="str">
@@ -31681,7 +31753,7 @@
       <x:c r="R507" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S507" s="9" t="n">
+      <x:c r="S507" s="9" t="str">
         <x:v>4330308</x:v>
       </x:c>
       <x:c r="T507" s="10" t="str">
@@ -31742,7 +31814,7 @@
       <x:c r="R508" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S508" s="9" t="n">
+      <x:c r="S508" s="9" t="str">
         <x:v>4330439</x:v>
       </x:c>
       <x:c r="T508" s="10" t="str">
@@ -31803,7 +31875,7 @@
       <x:c r="R509" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S509" s="9" t="n">
+      <x:c r="S509" s="9" t="str">
         <x:v>4330442</x:v>
       </x:c>
       <x:c r="T509" s="10" t="str">
@@ -31864,7 +31936,7 @@
       <x:c r="R510" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S510" s="9" t="n">
+      <x:c r="S510" s="9" t="str">
         <x:v>4528665</x:v>
       </x:c>
       <x:c r="T510" s="10" t="str">
@@ -31925,7 +31997,7 @@
       <x:c r="R511" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S511" s="9" t="n">
+      <x:c r="S511" s="9" t="str">
         <x:v>4814734</x:v>
       </x:c>
       <x:c r="T511" s="10" t="str">
@@ -31986,7 +32058,7 @@
       <x:c r="R512" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S512" s="9" t="n">
+      <x:c r="S512" s="9" t="str">
         <x:v>4814753</x:v>
       </x:c>
       <x:c r="T512" s="10" t="str">
@@ -32052,7 +32124,7 @@
       <x:c r="R513" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S513" s="9" t="n">
+      <x:c r="S513" s="9" t="str">
         <x:v>3741428</x:v>
       </x:c>
       <x:c r="T513" s="10" t="str">
@@ -32113,7 +32185,7 @@
       <x:c r="R514" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S514" s="9" t="n">
+      <x:c r="S514" s="9" t="str">
         <x:v>4330176</x:v>
       </x:c>
       <x:c r="T514" s="10" t="str">
@@ -32174,7 +32246,7 @@
       <x:c r="R515" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S515" s="9" t="n">
+      <x:c r="S515" s="9" t="str">
         <x:v>4528646</x:v>
       </x:c>
       <x:c r="T515" s="10" t="str">
@@ -32237,7 +32309,7 @@
       <x:c r="R516" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S516" s="9" t="n">
+      <x:c r="S516" s="9" t="str">
         <x:v>4529105</x:v>
       </x:c>
       <x:c r="T516" s="10" t="str">
@@ -32298,7 +32370,7 @@
       <x:c r="R517" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S517" s="9" t="n">
+      <x:c r="S517" s="9" t="str">
         <x:v>5154554</x:v>
       </x:c>
       <x:c r="T517" s="10" t="str">
@@ -32359,7 +32431,7 @@
       <x:c r="R518" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S518" s="9" t="n">
+      <x:c r="S518" s="9" t="str">
         <x:v>5155279</x:v>
       </x:c>
       <x:c r="T518" s="10" t="str">
@@ -32420,7 +32492,7 @@
       <x:c r="R519" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S519" s="9" t="n">
+      <x:c r="S519" s="9" t="str">
         <x:v>3768982</x:v>
       </x:c>
       <x:c r="T519" s="10" t="str">
@@ -32481,7 +32553,7 @@
       <x:c r="R520" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S520" s="9" t="n">
+      <x:c r="S520" s="9" t="str">
         <x:v>3769037</x:v>
       </x:c>
       <x:c r="T520" s="10" t="str">
@@ -32542,7 +32614,7 @@
       <x:c r="R521" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S521" s="9" t="n">
+      <x:c r="S521" s="9" t="str">
         <x:v>3786138</x:v>
       </x:c>
       <x:c r="T521" s="10" t="str">
@@ -32603,7 +32675,7 @@
       <x:c r="R522" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S522" s="9" t="n">
+      <x:c r="S522" s="9" t="str">
         <x:v>3786184</x:v>
       </x:c>
       <x:c r="T522" s="10" t="str">
@@ -32664,7 +32736,7 @@
       <x:c r="R523" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S523" s="9" t="n">
+      <x:c r="S523" s="9" t="str">
         <x:v>3787720</x:v>
       </x:c>
       <x:c r="T523" s="10" t="str">
@@ -32725,7 +32797,7 @@
       <x:c r="R524" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S524" s="9" t="n">
+      <x:c r="S524" s="9" t="str">
         <x:v>3787729</x:v>
       </x:c>
       <x:c r="T524" s="10" t="str">
@@ -32786,7 +32858,7 @@
       <x:c r="R525" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S525" s="9" t="n">
+      <x:c r="S525" s="9" t="str">
         <x:v>3789806</x:v>
       </x:c>
       <x:c r="T525" s="10" t="str">
@@ -32847,7 +32919,7 @@
       <x:c r="R526" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S526" s="9" t="n">
+      <x:c r="S526" s="9" t="str">
         <x:v>3789869</x:v>
       </x:c>
       <x:c r="T526" s="10" t="str">
@@ -32908,7 +32980,7 @@
       <x:c r="R527" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S527" s="9" t="n">
+      <x:c r="S527" s="9" t="str">
         <x:v>3790330</x:v>
       </x:c>
       <x:c r="T527" s="10" t="str">
@@ -32969,7 +33041,7 @@
       <x:c r="R528" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S528" s="9" t="n">
+      <x:c r="S528" s="9" t="str">
         <x:v>3790922</x:v>
       </x:c>
       <x:c r="T528" s="10" t="str">
@@ -33030,7 +33102,7 @@
       <x:c r="R529" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S529" s="9" t="n">
+      <x:c r="S529" s="9" t="str">
         <x:v>4814302</x:v>
       </x:c>
       <x:c r="T529" s="10" t="str">
@@ -33091,7 +33163,7 @@
       <x:c r="R530" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S530" s="9" t="n">
+      <x:c r="S530" s="9" t="str">
         <x:v>4814474</x:v>
       </x:c>
       <x:c r="T530" s="10" t="str">
@@ -33152,7 +33224,7 @@
       <x:c r="R531" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S531" s="9" t="n">
+      <x:c r="S531" s="9" t="str">
         <x:v>4814483</x:v>
       </x:c>
       <x:c r="T531" s="10" t="str">
@@ -33213,7 +33285,7 @@
       <x:c r="R532" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S532" s="9" t="n">
+      <x:c r="S532" s="9" t="str">
         <x:v>4814834</x:v>
       </x:c>
       <x:c r="T532" s="10" t="str">
@@ -33274,7 +33346,7 @@
       <x:c r="R533" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S533" s="9" t="n">
+      <x:c r="S533" s="9" t="str">
         <x:v>4814898</x:v>
       </x:c>
       <x:c r="T533" s="10" t="str">
@@ -33335,7 +33407,7 @@
       <x:c r="R534" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S534" s="9" t="n">
+      <x:c r="S534" s="9" t="str">
         <x:v>4814994</x:v>
       </x:c>
       <x:c r="T534" s="10" t="str">
@@ -33396,7 +33468,7 @@
       <x:c r="R535" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S535" s="9" t="n">
+      <x:c r="S535" s="9" t="str">
         <x:v>4815005</x:v>
       </x:c>
       <x:c r="T535" s="10" t="str">
@@ -33457,7 +33529,7 @@
       <x:c r="R536" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S536" s="9" t="n">
+      <x:c r="S536" s="9" t="str">
         <x:v>4815024</x:v>
       </x:c>
       <x:c r="T536" s="10" t="str">
@@ -33518,7 +33590,7 @@
       <x:c r="R537" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S537" s="9" t="n">
+      <x:c r="S537" s="9" t="str">
         <x:v>4815030</x:v>
       </x:c>
       <x:c r="T537" s="10" t="str">
@@ -33573,7 +33645,7 @@
       <x:c r="R538" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S538" s="9" t="n">
+      <x:c r="S538" s="9" t="str">
         <x:v>3742179</x:v>
       </x:c>
       <x:c r="T538" s="10" t="str">
@@ -33658,7 +33730,7 @@
       <x:c r="R539" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S539" s="9" t="n">
+      <x:c r="S539" s="9" t="str">
         <x:v>3743099</x:v>
       </x:c>
       <x:c r="T539" s="10" t="str">
@@ -33729,7 +33801,7 @@
       <x:c r="R540" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S540" s="9" t="n">
+      <x:c r="S540" s="9" t="str">
         <x:v>4330203</x:v>
       </x:c>
       <x:c r="T540" s="10" t="str">
@@ -33793,7 +33865,7 @@
       <x:c r="R541" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S541" s="9" t="n">
+      <x:c r="S541" s="9" t="str">
         <x:v>4330205</x:v>
       </x:c>
       <x:c r="T541" s="10" t="str">
@@ -33857,7 +33929,7 @@
       <x:c r="R542" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S542" s="9" t="n">
+      <x:c r="S542" s="9" t="str">
         <x:v>4330343</x:v>
       </x:c>
       <x:c r="T542" s="10" t="str">
@@ -33921,7 +33993,7 @@
       <x:c r="R543" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S543" s="9" t="n">
+      <x:c r="S543" s="9" t="str">
         <x:v>4330486</x:v>
       </x:c>
       <x:c r="T543" s="10" t="str">
@@ -33985,7 +34057,7 @@
       <x:c r="R544" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S544" s="9" t="n">
+      <x:c r="S544" s="9" t="str">
         <x:v>4324454</x:v>
       </x:c>
       <x:c r="T544" s="10" t="str">
@@ -34049,7 +34121,7 @@
       <x:c r="R545" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S545" s="9" t="n">
+      <x:c r="S545" s="9" t="str">
         <x:v>3787048</x:v>
       </x:c>
       <x:c r="T545" s="10" t="str">
@@ -34113,7 +34185,7 @@
       <x:c r="R546" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S546" s="9" t="n">
+      <x:c r="S546" s="9" t="str">
         <x:v>3787858</x:v>
       </x:c>
       <x:c r="T546" s="10" t="str">
@@ -34177,7 +34249,7 @@
       <x:c r="R547" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S547" s="9" t="n">
+      <x:c r="S547" s="9" t="str">
         <x:v>3790078</x:v>
       </x:c>
       <x:c r="T547" s="10" t="str">
@@ -34241,7 +34313,7 @@
       <x:c r="R548" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S548" s="9" t="n">
+      <x:c r="S548" s="9" t="str">
         <x:v>3790094</x:v>
       </x:c>
       <x:c r="T548" s="10" t="str">
@@ -34305,7 +34377,7 @@
       <x:c r="R549" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S549" s="9" t="n">
+      <x:c r="S549" s="9" t="str">
         <x:v>3791055</x:v>
       </x:c>
       <x:c r="T549" s="10" t="str">
@@ -34373,7 +34445,7 @@
       <x:c r="R550" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S550" s="9" t="n">
+      <x:c r="S550" s="9" t="str">
         <x:v>4528575</x:v>
       </x:c>
       <x:c r="T550" s="10" t="str">
@@ -34438,7 +34510,7 @@
       <x:c r="R551" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S551" s="9" t="n">
+      <x:c r="S551" s="9" t="str">
         <x:v>4529174</x:v>
       </x:c>
       <x:c r="T551" s="10" t="str">
@@ -34502,7 +34574,7 @@
       <x:c r="R552" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S552" s="9" t="n">
+      <x:c r="S552" s="9" t="str">
         <x:v>4814369</x:v>
       </x:c>
       <x:c r="T552" s="10" t="str">
@@ -34566,7 +34638,7 @@
       <x:c r="R553" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S553" s="9" t="n">
+      <x:c r="S553" s="9" t="str">
         <x:v>4814924</x:v>
       </x:c>
       <x:c r="T553" s="10" t="str">
@@ -34630,7 +34702,7 @@
       <x:c r="R554" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S554" s="9" t="n">
+      <x:c r="S554" s="9" t="str">
         <x:v>4814935</x:v>
       </x:c>
       <x:c r="T554" s="10" t="str">
@@ -34685,7 +34757,7 @@
       <x:c r="R555" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S555" s="9" t="n">
+      <x:c r="S555" s="9" t="str">
         <x:v>4324685</x:v>
       </x:c>
       <x:c r="T555" s="10" t="str">
@@ -34740,7 +34812,7 @@
       <x:c r="R556" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S556" s="9" t="n">
+      <x:c r="S556" s="9" t="str">
         <x:v>4324688</x:v>
       </x:c>
       <x:c r="T556" s="10" t="str">
@@ -34795,7 +34867,7 @@
       <x:c r="R557" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S557" s="9" t="n">
+      <x:c r="S557" s="9" t="str">
         <x:v>4324692</x:v>
       </x:c>
       <x:c r="T557" s="10" t="str">
@@ -34850,7 +34922,7 @@
       <x:c r="R558" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S558" s="9" t="n">
+      <x:c r="S558" s="9" t="str">
         <x:v>4324693</x:v>
       </x:c>
       <x:c r="T558" s="10" t="str">
@@ -34905,7 +34977,7 @@
       <x:c r="R559" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S559" s="9" t="n">
+      <x:c r="S559" s="9" t="str">
         <x:v>4330234</x:v>
       </x:c>
       <x:c r="T559" s="10" t="str">
@@ -34960,7 +35032,7 @@
       <x:c r="R560" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S560" s="9" t="n">
+      <x:c r="S560" s="9" t="str">
         <x:v>4330513</x:v>
       </x:c>
       <x:c r="T560" s="10" t="str">
@@ -35015,7 +35087,7 @@
       <x:c r="R561" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S561" s="9" t="n">
+      <x:c r="S561" s="9" t="str">
         <x:v>4814810</x:v>
       </x:c>
       <x:c r="T561" s="10" t="str">
@@ -35070,7 +35142,7 @@
       <x:c r="R562" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S562" s="9" t="n">
+      <x:c r="S562" s="9" t="str">
         <x:v>4815084</x:v>
       </x:c>
       <x:c r="T562" s="10" t="str">
@@ -35125,7 +35197,7 @@
       <x:c r="R563" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S563" s="9" t="n">
+      <x:c r="S563" s="9" t="str">
         <x:v>4815099</x:v>
       </x:c>
       <x:c r="T563" s="10" t="str">
@@ -35191,7 +35263,7 @@
       <x:c r="R564" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S564" s="9" t="n">
+      <x:c r="S564" s="9" t="str">
         <x:v>3741702</x:v>
       </x:c>
       <x:c r="T564" s="10" t="str">
@@ -35247,12 +35319,13 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="Q565" s="9" t="str">
-        <x:v>[图片: https://file.233.com/ess-files/ess-bms-web/fiex/couser/2023/9/13/2FA9AB10DB124FE2A152EE0F2EACE8B0.png]</x:v>
+        <x:v>贷款风险分类规则中，“未经商业银行同意，擅自改变资金用途”的最低分类级次为关注类。
+故本题选B。</x:v>
       </x:c>
       <x:c r="R565" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S565" s="9" t="n">
+      <x:c r="S565" s="9" t="str">
         <x:v>4324701</x:v>
       </x:c>
       <x:c r="T565" s="10" t="str">
@@ -35313,7 +35386,7 @@
       <x:c r="R566" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S566" s="9" t="n">
+      <x:c r="S566" s="9" t="str">
         <x:v>4330444</x:v>
       </x:c>
       <x:c r="T566" s="10" t="str">
@@ -35374,7 +35447,7 @@
       <x:c r="R567" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S567" s="9" t="n">
+      <x:c r="S567" s="9" t="str">
         <x:v>3731123</x:v>
       </x:c>
       <x:c r="T567" s="10" t="str">
@@ -35435,7 +35508,7 @@
       <x:c r="R568" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S568" s="9" t="n">
+      <x:c r="S568" s="9" t="str">
         <x:v>3731128</x:v>
       </x:c>
       <x:c r="T568" s="10" t="str">
@@ -35496,7 +35569,7 @@
       <x:c r="R569" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S569" s="9" t="n">
+      <x:c r="S569" s="9" t="str">
         <x:v>3787800</x:v>
       </x:c>
       <x:c r="T569" s="10" t="str">
@@ -35557,7 +35630,7 @@
       <x:c r="R570" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S570" s="9" t="n">
+      <x:c r="S570" s="9" t="str">
         <x:v>3790715</x:v>
       </x:c>
       <x:c r="T570" s="10" t="str">
@@ -35622,7 +35695,7 @@
       <x:c r="R571" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S571" s="9" t="n">
+      <x:c r="S571" s="9" t="str">
         <x:v>3790761</x:v>
       </x:c>
       <x:c r="T571" s="10" t="str">
@@ -35683,7 +35756,7 @@
       <x:c r="R572" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S572" s="9" t="n">
+      <x:c r="S572" s="9" t="str">
         <x:v>4528520</x:v>
       </x:c>
       <x:c r="T572" s="10" t="str">
@@ -35744,7 +35817,7 @@
       <x:c r="R573" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S573" s="9" t="n">
+      <x:c r="S573" s="9" t="str">
         <x:v>4814837</x:v>
       </x:c>
       <x:c r="T573" s="10" t="str">
@@ -35808,7 +35881,7 @@
       <x:c r="R574" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S574" s="9" t="n">
+      <x:c r="S574" s="9" t="str">
         <x:v>4330492</x:v>
       </x:c>
       <x:c r="T574" s="10" t="str">
@@ -35872,7 +35945,7 @@
       <x:c r="R575" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S575" s="9" t="n">
+      <x:c r="S575" s="9" t="str">
         <x:v>4324714</x:v>
       </x:c>
       <x:c r="T575" s="10" t="str">
@@ -35937,7 +36010,7 @@
       <x:c r="R576" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S576" s="9" t="n">
+      <x:c r="S576" s="9" t="str">
         <x:v>4330345</x:v>
       </x:c>
       <x:c r="T576" s="10" t="str">
@@ -36001,7 +36074,7 @@
       <x:c r="R577" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S577" s="9" t="n">
+      <x:c r="S577" s="9" t="str">
         <x:v>4330493</x:v>
       </x:c>
       <x:c r="T577" s="10" t="str">
@@ -36072,7 +36145,7 @@
       <x:c r="R578" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S578" s="9" t="n">
+      <x:c r="S578" s="9" t="str">
         <x:v>4529169</x:v>
       </x:c>
       <x:c r="T578" s="10" t="str">
@@ -36136,7 +36209,7 @@
       <x:c r="R579" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S579" s="9" t="n">
+      <x:c r="S579" s="9" t="str">
         <x:v>4815055</x:v>
       </x:c>
       <x:c r="T579" s="10" t="str">
@@ -36197,7 +36270,7 @@
       <x:c r="R580" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S580" s="9" t="n">
+      <x:c r="S580" s="9" t="str">
         <x:v>3731379</x:v>
       </x:c>
       <x:c r="T580" s="10" t="str">
@@ -36258,7 +36331,7 @@
       <x:c r="R581" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S581" s="9" t="n">
+      <x:c r="S581" s="9" t="str">
         <x:v>3742059</x:v>
       </x:c>
       <x:c r="T581" s="10" t="str">
@@ -36319,7 +36392,7 @@
       <x:c r="R582" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S582" s="9" t="n">
+      <x:c r="S582" s="9" t="str">
         <x:v>4324719</x:v>
       </x:c>
       <x:c r="T582" s="10" t="str">
@@ -36380,7 +36453,7 @@
       <x:c r="R583" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S583" s="9" t="n">
+      <x:c r="S583" s="9" t="str">
         <x:v>4324722</x:v>
       </x:c>
       <x:c r="T583" s="10" t="str">
@@ -36441,7 +36514,7 @@
       <x:c r="R584" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S584" s="9" t="n">
+      <x:c r="S584" s="9" t="str">
         <x:v>4324724</x:v>
       </x:c>
       <x:c r="T584" s="10" t="str">
@@ -36502,7 +36575,7 @@
       <x:c r="R585" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S585" s="9" t="n">
+      <x:c r="S585" s="9" t="str">
         <x:v>4324729</x:v>
       </x:c>
       <x:c r="T585" s="10" t="str">
@@ -36563,7 +36636,7 @@
       <x:c r="R586" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S586" s="9" t="n">
+      <x:c r="S586" s="9" t="str">
         <x:v>4324731</x:v>
       </x:c>
       <x:c r="T586" s="10" t="str">
@@ -36624,7 +36697,7 @@
       <x:c r="R587" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S587" s="9" t="n">
+      <x:c r="S587" s="9" t="str">
         <x:v>4330452</x:v>
       </x:c>
       <x:c r="T587" s="10" t="str">
@@ -36685,7 +36758,7 @@
       <x:c r="R588" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S588" s="9" t="n">
+      <x:c r="S588" s="9" t="str">
         <x:v>4330454</x:v>
       </x:c>
       <x:c r="T588" s="10" t="str">
@@ -36746,7 +36819,7 @@
       <x:c r="R589" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S589" s="9" t="n">
+      <x:c r="S589" s="9" t="str">
         <x:v>4814738</x:v>
       </x:c>
       <x:c r="T589" s="10" t="str">
@@ -36807,7 +36880,7 @@
       <x:c r="R590" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S590" s="9" t="n">
+      <x:c r="S590" s="9" t="str">
         <x:v>3741705</x:v>
       </x:c>
       <x:c r="T590" s="10" t="str">
@@ -36868,7 +36941,7 @@
       <x:c r="R591" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S591" s="9" t="n">
+      <x:c r="S591" s="9" t="str">
         <x:v>4324726</x:v>
       </x:c>
       <x:c r="T591" s="10" t="str">
@@ -36929,7 +37002,7 @@
       <x:c r="R592" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S592" s="9" t="n">
+      <x:c r="S592" s="9" t="str">
         <x:v>3790311</x:v>
       </x:c>
       <x:c r="T592" s="10" t="str">
@@ -36990,7 +37063,7 @@
       <x:c r="R593" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S593" s="9" t="n">
+      <x:c r="S593" s="9" t="str">
         <x:v>3790321</x:v>
       </x:c>
       <x:c r="T593" s="10" t="str">
@@ -37051,7 +37124,7 @@
       <x:c r="R594" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S594" s="9" t="n">
+      <x:c r="S594" s="9" t="str">
         <x:v>3790702</x:v>
       </x:c>
       <x:c r="T594" s="10" t="str">
@@ -37112,7 +37185,7 @@
       <x:c r="R595" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S595" s="9" t="n">
+      <x:c r="S595" s="9" t="str">
         <x:v>3790703</x:v>
       </x:c>
       <x:c r="T595" s="10" t="str">
@@ -37173,7 +37246,7 @@
       <x:c r="R596" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S596" s="9" t="n">
+      <x:c r="S596" s="9" t="str">
         <x:v>3790709</x:v>
       </x:c>
       <x:c r="T596" s="10" t="str">
@@ -37234,7 +37307,7 @@
       <x:c r="R597" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S597" s="9" t="n">
+      <x:c r="S597" s="9" t="str">
         <x:v>3790718</x:v>
       </x:c>
       <x:c r="T597" s="10" t="str">
@@ -37295,7 +37368,7 @@
       <x:c r="R598" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S598" s="9" t="n">
+      <x:c r="S598" s="9" t="str">
         <x:v>3790719</x:v>
       </x:c>
       <x:c r="T598" s="10" t="str">
@@ -37356,7 +37429,7 @@
       <x:c r="R599" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S599" s="9" t="n">
+      <x:c r="S599" s="9" t="str">
         <x:v>3790720</x:v>
       </x:c>
       <x:c r="T599" s="10" t="str">
@@ -37417,7 +37490,7 @@
       <x:c r="R600" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S600" s="9" t="n">
+      <x:c r="S600" s="9" t="str">
         <x:v>4528481</x:v>
       </x:c>
       <x:c r="T600" s="10" t="str">
@@ -37478,7 +37551,7 @@
       <x:c r="R601" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S601" s="9" t="n">
+      <x:c r="S601" s="9" t="str">
         <x:v>4529059</x:v>
       </x:c>
       <x:c r="T601" s="10" t="str">
@@ -37539,7 +37612,7 @@
       <x:c r="R602" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S602" s="9" t="n">
+      <x:c r="S602" s="9" t="str">
         <x:v>4529070</x:v>
       </x:c>
       <x:c r="T602" s="10" t="str">
@@ -37600,7 +37673,7 @@
       <x:c r="R603" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S603" s="9" t="n">
+      <x:c r="S603" s="9" t="str">
         <x:v>4529124</x:v>
       </x:c>
       <x:c r="T603" s="10" t="str">
@@ -37661,7 +37734,7 @@
       <x:c r="R604" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S604" s="9" t="n">
+      <x:c r="S604" s="9" t="str">
         <x:v>4814271</x:v>
       </x:c>
       <x:c r="T604" s="10" t="str">
@@ -37722,7 +37795,7 @@
       <x:c r="R605" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S605" s="9" t="n">
+      <x:c r="S605" s="9" t="str">
         <x:v>4814485</x:v>
       </x:c>
       <x:c r="T605" s="10" t="str">
@@ -37783,7 +37856,7 @@
       <x:c r="R606" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S606" s="9" t="n">
+      <x:c r="S606" s="9" t="str">
         <x:v>4814489</x:v>
       </x:c>
       <x:c r="T606" s="10" t="str">
@@ -37844,7 +37917,7 @@
       <x:c r="R607" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S607" s="9" t="n">
+      <x:c r="S607" s="9" t="str">
         <x:v>4814490</x:v>
       </x:c>
       <x:c r="T607" s="10" t="str">
@@ -37905,7 +37978,7 @@
       <x:c r="R608" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S608" s="9" t="n">
+      <x:c r="S608" s="9" t="str">
         <x:v>4814981</x:v>
       </x:c>
       <x:c r="T608" s="10" t="str">
@@ -37966,7 +38039,7 @@
       <x:c r="R609" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S609" s="9" t="n">
+      <x:c r="S609" s="9" t="str">
         <x:v>4814984</x:v>
       </x:c>
       <x:c r="T609" s="10" t="str">
@@ -38021,7 +38094,7 @@
       <x:c r="R610" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S610" s="9" t="n">
+      <x:c r="S610" s="9" t="str">
         <x:v>5099008</x:v>
       </x:c>
       <x:c r="T610" s="10" t="str">
@@ -38085,7 +38158,7 @@
       <x:c r="R611" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S611" s="9" t="n">
+      <x:c r="S611" s="9" t="str">
         <x:v>4324736</x:v>
       </x:c>
       <x:c r="T611" s="10" t="str">
@@ -38149,7 +38222,7 @@
       <x:c r="R612" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S612" s="9" t="n">
+      <x:c r="S612" s="9" t="str">
         <x:v>4330212</x:v>
       </x:c>
       <x:c r="T612" s="10" t="str">
@@ -38213,7 +38286,7 @@
       <x:c r="R613" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S613" s="9" t="n">
+      <x:c r="S613" s="9" t="str">
         <x:v>4330213</x:v>
       </x:c>
       <x:c r="T613" s="10" t="str">
@@ -38277,7 +38350,7 @@
       <x:c r="R614" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S614" s="9" t="n">
+      <x:c r="S614" s="9" t="str">
         <x:v>4330214</x:v>
       </x:c>
       <x:c r="T614" s="10" t="str">
@@ -38341,7 +38414,7 @@
       <x:c r="R615" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S615" s="9" t="n">
+      <x:c r="S615" s="9" t="str">
         <x:v>4814793</x:v>
       </x:c>
       <x:c r="T615" s="10" t="str">
@@ -38405,7 +38478,7 @@
       <x:c r="R616" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S616" s="9" t="n">
+      <x:c r="S616" s="9" t="str">
         <x:v>4330496</x:v>
       </x:c>
       <x:c r="T616" s="10" t="str">
@@ -38469,7 +38542,7 @@
       <x:c r="R617" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S617" s="9" t="n">
+      <x:c r="S617" s="9" t="str">
         <x:v>3791078</x:v>
       </x:c>
       <x:c r="T617" s="10" t="str">
@@ -38533,7 +38606,7 @@
       <x:c r="R618" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S618" s="9" t="n">
+      <x:c r="S618" s="9" t="str">
         <x:v>4528554</x:v>
       </x:c>
       <x:c r="T618" s="10" t="str">
@@ -38597,7 +38670,7 @@
       <x:c r="R619" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S619" s="9" t="n">
+      <x:c r="S619" s="9" t="str">
         <x:v>4528691</x:v>
       </x:c>
       <x:c r="T619" s="10" t="str">
@@ -38661,7 +38734,7 @@
       <x:c r="R620" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S620" s="9" t="n">
+      <x:c r="S620" s="9" t="str">
         <x:v>4528898</x:v>
       </x:c>
       <x:c r="T620" s="10" t="str">
@@ -38725,7 +38798,7 @@
       <x:c r="R621" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S621" s="9" t="n">
+      <x:c r="S621" s="9" t="str">
         <x:v>4528904</x:v>
       </x:c>
       <x:c r="T621" s="10" t="str">
@@ -38792,7 +38865,7 @@
       <x:c r="R622" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S622" s="9" t="n">
+      <x:c r="S622" s="9" t="str">
         <x:v>4529167</x:v>
       </x:c>
       <x:c r="T622" s="10" t="str">
@@ -38856,7 +38929,7 @@
       <x:c r="R623" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S623" s="9" t="n">
+      <x:c r="S623" s="9" t="str">
         <x:v>4814365</x:v>
       </x:c>
       <x:c r="T623" s="10" t="str">
@@ -38920,7 +38993,7 @@
       <x:c r="R624" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S624" s="9" t="n">
+      <x:c r="S624" s="9" t="str">
         <x:v>4814397</x:v>
       </x:c>
       <x:c r="T624" s="10" t="str">
@@ -38984,7 +39057,7 @@
       <x:c r="R625" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S625" s="9" t="n">
+      <x:c r="S625" s="9" t="str">
         <x:v>4814620</x:v>
       </x:c>
       <x:c r="T625" s="10" t="str">
@@ -39048,7 +39121,7 @@
       <x:c r="R626" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S626" s="9" t="n">
+      <x:c r="S626" s="9" t="str">
         <x:v>4814929</x:v>
       </x:c>
       <x:c r="T626" s="10" t="str">
@@ -39103,7 +39176,7 @@
       <x:c r="R627" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S627" s="9" t="n">
+      <x:c r="S627" s="9" t="str">
         <x:v>4324748</x:v>
       </x:c>
       <x:c r="T627" s="10" t="str">
@@ -39158,7 +39231,7 @@
       <x:c r="R628" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S628" s="9" t="n">
+      <x:c r="S628" s="9" t="str">
         <x:v>4324751</x:v>
       </x:c>
       <x:c r="T628" s="10" t="str">
@@ -39219,7 +39292,7 @@
       <x:c r="R629" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S629" s="9" t="n">
+      <x:c r="S629" s="9" t="str">
         <x:v>3731070</x:v>
       </x:c>
       <x:c r="T629" s="10" t="str">
@@ -39280,7 +39353,7 @@
       <x:c r="R630" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S630" s="9" t="n">
+      <x:c r="S630" s="9" t="str">
         <x:v>3731297</x:v>
       </x:c>
       <x:c r="T630" s="10" t="str">
@@ -39341,7 +39414,7 @@
       <x:c r="R631" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S631" s="9" t="n">
+      <x:c r="S631" s="9" t="str">
         <x:v>3731455</x:v>
       </x:c>
       <x:c r="T631" s="10" t="str">
@@ -39402,7 +39475,7 @@
       <x:c r="R632" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S632" s="9" t="n">
+      <x:c r="S632" s="9" t="str">
         <x:v>4324507</x:v>
       </x:c>
       <x:c r="T632" s="10" t="str">
@@ -39463,7 +39536,7 @@
       <x:c r="R633" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S633" s="9" t="n">
+      <x:c r="S633" s="9" t="str">
         <x:v>4330258</x:v>
       </x:c>
       <x:c r="T633" s="10" t="str">
@@ -39524,7 +39597,7 @@
       <x:c r="R634" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S634" s="9" t="n">
+      <x:c r="S634" s="9" t="str">
         <x:v>4330263</x:v>
       </x:c>
       <x:c r="T634" s="10" t="str">
@@ -39585,7 +39658,7 @@
       <x:c r="R635" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S635" s="9" t="n">
+      <x:c r="S635" s="9" t="str">
         <x:v>4330400</x:v>
       </x:c>
       <x:c r="T635" s="10" t="str">
@@ -39647,7 +39720,7 @@
       <x:c r="R636" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S636" s="9" t="n">
+      <x:c r="S636" s="9" t="str">
         <x:v>4529109</x:v>
       </x:c>
       <x:c r="T636" s="10" t="str">
@@ -39709,7 +39782,7 @@
       <x:c r="R637" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S637" s="9" t="n">
+      <x:c r="S637" s="9" t="str">
         <x:v>5087843</x:v>
       </x:c>
       <x:c r="T637" s="10" t="str">
@@ -39773,7 +39846,7 @@
       <x:c r="R638" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S638" s="9" t="n">
+      <x:c r="S638" s="9" t="str">
         <x:v>6900488</x:v>
       </x:c>
       <x:c r="T638" s="10" t="str">
@@ -39834,7 +39907,7 @@
       <x:c r="R639" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S639" s="9" t="n">
+      <x:c r="S639" s="9" t="str">
         <x:v>3731108</x:v>
       </x:c>
       <x:c r="T639" s="10" t="str">
@@ -39895,7 +39968,7 @@
       <x:c r="R640" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S640" s="9" t="n">
+      <x:c r="S640" s="9" t="str">
         <x:v>3786171</x:v>
       </x:c>
       <x:c r="T640" s="10" t="str">
@@ -39956,7 +40029,7 @@
       <x:c r="R641" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S641" s="9" t="n">
+      <x:c r="S641" s="9" t="str">
         <x:v>4528476</x:v>
       </x:c>
       <x:c r="T641" s="10" t="str">
@@ -40017,7 +40090,7 @@
       <x:c r="R642" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S642" s="9" t="n">
+      <x:c r="S642" s="9" t="str">
         <x:v>4528614</x:v>
       </x:c>
       <x:c r="T642" s="10" t="str">
@@ -40079,7 +40152,7 @@
       <x:c r="R643" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S643" s="9" t="n">
+      <x:c r="S643" s="9" t="str">
         <x:v>4529108</x:v>
       </x:c>
       <x:c r="T643" s="10" t="str">
@@ -40140,7 +40213,7 @@
       <x:c r="R644" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S644" s="9" t="n">
+      <x:c r="S644" s="9" t="str">
         <x:v>4814849</x:v>
       </x:c>
       <x:c r="T644" s="10" t="str">
@@ -40201,7 +40274,7 @@
       <x:c r="R645" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S645" s="9" t="n">
+      <x:c r="S645" s="9" t="str">
         <x:v>4814870</x:v>
       </x:c>
       <x:c r="T645" s="10" t="str">
@@ -40262,7 +40335,7 @@
       <x:c r="R646" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S646" s="9" t="n">
+      <x:c r="S646" s="9" t="str">
         <x:v>4814962</x:v>
       </x:c>
       <x:c r="T646" s="10" t="str">
@@ -40323,7 +40396,7 @@
       <x:c r="R647" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S647" s="9" t="n">
+      <x:c r="S647" s="9" t="str">
         <x:v>4815006</x:v>
       </x:c>
       <x:c r="T647" s="10" t="str">
@@ -40384,7 +40457,7 @@
       <x:c r="R648" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S648" s="9" t="n">
+      <x:c r="S648" s="9" t="str">
         <x:v>4815009</x:v>
       </x:c>
       <x:c r="T648" s="10" t="str">
@@ -40445,7 +40518,7 @@
       <x:c r="R649" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S649" s="9" t="n">
+      <x:c r="S649" s="9" t="str">
         <x:v>4815027</x:v>
       </x:c>
       <x:c r="T649" s="10" t="str">
@@ -40506,7 +40579,7 @@
       <x:c r="R650" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S650" s="9" t="n">
+      <x:c r="S650" s="9" t="str">
         <x:v>6900469</x:v>
       </x:c>
       <x:c r="T650" s="10" t="str">
@@ -40567,7 +40640,7 @@
       <x:c r="R651" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S651" s="9" t="n">
+      <x:c r="S651" s="9" t="str">
         <x:v>6900470</x:v>
       </x:c>
       <x:c r="T651" s="10" t="str">
@@ -40628,7 +40701,7 @@
       <x:c r="R652" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S652" s="9" t="n">
+      <x:c r="S652" s="9" t="str">
         <x:v>6900472</x:v>
       </x:c>
       <x:c r="T652" s="10" t="str">
@@ -40689,7 +40762,7 @@
       <x:c r="R653" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S653" s="9" t="n">
+      <x:c r="S653" s="9" t="str">
         <x:v>6900473</x:v>
       </x:c>
       <x:c r="T653" s="10" t="str">
@@ -40750,7 +40823,7 @@
       <x:c r="R654" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S654" s="9" t="n">
+      <x:c r="S654" s="9" t="str">
         <x:v>6900475</x:v>
       </x:c>
       <x:c r="T654" s="10" t="str">
@@ -40805,7 +40878,7 @@
       <x:c r="R655" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S655" s="9" t="n">
+      <x:c r="S655" s="9" t="str">
         <x:v>3741523</x:v>
       </x:c>
       <x:c r="T655" s="10" t="str">
@@ -40860,7 +40933,7 @@
       <x:c r="R656" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S656" s="9" t="n">
+      <x:c r="S656" s="9" t="str">
         <x:v>3741874</x:v>
       </x:c>
       <x:c r="T656" s="10" t="str">
@@ -40915,7 +40988,7 @@
       <x:c r="R657" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S657" s="9" t="n">
+      <x:c r="S657" s="9" t="str">
         <x:v>5087847</x:v>
       </x:c>
       <x:c r="T657" s="10" t="str">
@@ -40979,7 +41052,7 @@
       <x:c r="R658" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S658" s="9" t="n">
+      <x:c r="S658" s="9" t="str">
         <x:v>3741506</x:v>
       </x:c>
       <x:c r="T658" s="10" t="str">
@@ -41043,7 +41116,7 @@
       <x:c r="R659" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S659" s="9" t="n">
+      <x:c r="S659" s="9" t="str">
         <x:v>4324451</x:v>
       </x:c>
       <x:c r="T659" s="10" t="str">
@@ -41107,7 +41180,7 @@
       <x:c r="R660" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S660" s="9" t="n">
+      <x:c r="S660" s="9" t="str">
         <x:v>4330356</x:v>
       </x:c>
       <x:c r="T660" s="10" t="str">
@@ -41171,7 +41244,7 @@
       <x:c r="R661" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S661" s="9" t="n">
+      <x:c r="S661" s="9" t="str">
         <x:v>4814789</x:v>
       </x:c>
       <x:c r="T661" s="10" t="str">
@@ -41239,7 +41312,7 @@
       <x:c r="R662" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S662" s="9" t="n">
+      <x:c r="S662" s="9" t="str">
         <x:v>5087842</x:v>
       </x:c>
       <x:c r="T662" s="10" t="str">
@@ -41303,7 +41376,7 @@
       <x:c r="R663" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S663" s="9" t="n">
+      <x:c r="S663" s="9" t="str">
         <x:v>6900489</x:v>
       </x:c>
       <x:c r="T663" s="10" t="str">
@@ -41367,7 +41440,7 @@
       <x:c r="R664" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S664" s="9" t="n">
+      <x:c r="S664" s="9" t="str">
         <x:v>6900503</x:v>
       </x:c>
       <x:c r="T664" s="10" t="str">
@@ -41431,7 +41504,7 @@
       <x:c r="R665" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S665" s="9" t="n">
+      <x:c r="S665" s="9" t="str">
         <x:v>6900504</x:v>
       </x:c>
       <x:c r="T665" s="10" t="str">
@@ -41495,7 +41568,7 @@
       <x:c r="R666" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S666" s="9" t="n">
+      <x:c r="S666" s="9" t="str">
         <x:v>4814781</x:v>
       </x:c>
       <x:c r="T666" s="10" t="str">
@@ -41559,7 +41632,7 @@
       <x:c r="R667" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S667" s="9" t="n">
+      <x:c r="S667" s="9" t="str">
         <x:v>4814796</x:v>
       </x:c>
       <x:c r="T667" s="10" t="str">
@@ -41626,7 +41699,7 @@
       <x:c r="R668" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S668" s="9" t="n">
+      <x:c r="S668" s="9" t="str">
         <x:v>5087841</x:v>
       </x:c>
       <x:c r="T668" s="10" t="str">
@@ -41690,7 +41763,7 @@
       <x:c r="R669" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S669" s="9" t="n">
+      <x:c r="S669" s="9" t="str">
         <x:v>6900486</x:v>
       </x:c>
       <x:c r="T669" s="10" t="str">
@@ -41754,7 +41827,7 @@
       <x:c r="R670" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S670" s="9" t="n">
+      <x:c r="S670" s="9" t="str">
         <x:v>3787829</x:v>
       </x:c>
       <x:c r="T670" s="10" t="str">
@@ -41818,7 +41891,7 @@
       <x:c r="R671" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S671" s="9" t="n">
+      <x:c r="S671" s="9" t="str">
         <x:v>4528572</x:v>
       </x:c>
       <x:c r="T671" s="10" t="str">
@@ -41889,7 +41962,7 @@
       <x:c r="R672" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S672" s="9" t="n">
+      <x:c r="S672" s="9" t="str">
         <x:v>4529161</x:v>
       </x:c>
       <x:c r="T672" s="10" t="str">
@@ -41961,7 +42034,7 @@
       <x:c r="R673" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S673" s="9" t="n">
+      <x:c r="S673" s="9" t="str">
         <x:v>4529164</x:v>
       </x:c>
       <x:c r="T673" s="10" t="str">
@@ -42026,7 +42099,7 @@
       <x:c r="R674" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S674" s="9" t="n">
+      <x:c r="S674" s="9" t="str">
         <x:v>4529170</x:v>
       </x:c>
       <x:c r="T674" s="10" t="str">
@@ -42090,7 +42163,7 @@
       <x:c r="R675" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S675" s="9" t="n">
+      <x:c r="S675" s="9" t="str">
         <x:v>4814903</x:v>
       </x:c>
       <x:c r="T675" s="10" t="str">
@@ -42154,7 +42227,7 @@
       <x:c r="R676" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S676" s="9" t="n">
+      <x:c r="S676" s="9" t="str">
         <x:v>4814904</x:v>
       </x:c>
       <x:c r="T676" s="10" t="str">
@@ -42218,7 +42291,7 @@
       <x:c r="R677" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S677" s="9" t="n">
+      <x:c r="S677" s="9" t="str">
         <x:v>4815063</x:v>
       </x:c>
       <x:c r="T677" s="10" t="str">
@@ -42282,7 +42355,7 @@
       <x:c r="R678" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S678" s="9" t="n">
+      <x:c r="S678" s="9" t="str">
         <x:v>6900471</x:v>
       </x:c>
       <x:c r="T678" s="10" t="str">
@@ -42337,7 +42410,7 @@
       <x:c r="R679" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S679" s="9" t="n">
+      <x:c r="S679" s="9" t="str">
         <x:v>4324459</x:v>
       </x:c>
       <x:c r="T679" s="10" t="str">
@@ -42397,7 +42470,7 @@
       <x:c r="R680" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S680" s="9" t="n">
+      <x:c r="S680" s="9" t="str">
         <x:v>6900490</x:v>
       </x:c>
       <x:c r="T680" s="10" t="str">
@@ -42452,7 +42525,7 @@
       <x:c r="R681" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S681" s="9" t="n">
+      <x:c r="S681" s="9" t="str">
         <x:v>6900491</x:v>
       </x:c>
       <x:c r="T681" s="10" t="str">
@@ -42507,7 +42580,7 @@
       <x:c r="R682" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S682" s="9" t="n">
+      <x:c r="S682" s="9" t="str">
         <x:v>6900502</x:v>
       </x:c>
       <x:c r="T682" s="10" t="str">
@@ -42562,7 +42635,7 @@
       <x:c r="R683" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S683" s="9" t="n">
+      <x:c r="S683" s="9" t="str">
         <x:v>6900505</x:v>
       </x:c>
       <x:c r="T683" s="10" t="str">
@@ -42617,7 +42690,7 @@
       <x:c r="R684" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S684" s="9" t="n">
+      <x:c r="S684" s="9" t="str">
         <x:v>6900487</x:v>
       </x:c>
       <x:c r="T684" s="10" t="str">
@@ -42672,7 +42745,7 @@
       <x:c r="R685" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S685" s="9" t="n">
+      <x:c r="S685" s="9" t="str">
         <x:v>4814957</x:v>
       </x:c>
       <x:c r="T685" s="10" t="str">
@@ -42727,7 +42800,7 @@
       <x:c r="R686" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S686" s="9" t="n">
+      <x:c r="S686" s="9" t="str">
         <x:v>4815082</x:v>
       </x:c>
       <x:c r="T686" s="10" t="str">
@@ -42782,7 +42855,7 @@
       <x:c r="R687" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S687" s="9" t="n">
+      <x:c r="S687" s="9" t="str">
         <x:v>4815087</x:v>
       </x:c>
       <x:c r="T687" s="10" t="str">
@@ -42837,7 +42910,7 @@
       <x:c r="R688" s="12" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S688" s="12" t="n">
+      <x:c r="S688" s="12" t="str">
         <x:v>6900474</x:v>
       </x:c>
       <x:c r="T688" s="13" t="str">
@@ -42860,6 +42933,7 @@
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -42876,12 +42950,15 @@
         <x:v>预计题量</x:v>
       </x:c>
       <x:c r="E1" s="27" t="str">
+        <x:v>接口题量</x:v>
+      </x:c>
+      <x:c r="F1" s="27" t="str">
         <x:v>抓取题量</x:v>
       </x:c>
-      <x:c r="F1" s="27" t="str">
+      <x:c r="G1" s="27" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="G1" s="28" t="str">
+      <x:c r="H1" s="28" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
     </x:row>
@@ -42892,19 +42969,22 @@
       <x:c r="B2" s="9" t="str">
         <x:v>第一章 公司信贷概述</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="n">
+      <x:c r="C2" s="9" t="str">
         <x:v>62493</x:v>
       </x:c>
-      <x:c r="D2" s="9" t="n">
+      <x:c r="D2" s="29" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E2" s="9" t="n">
+      <x:c r="E2" s="29" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F2" s="9" t="n">
+      <x:c r="F2" s="29" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G2" s="29" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="n">
+      <x:c r="H2" s="30" t="n">
         <x:v>34</x:v>
       </x:c>
     </x:row>
@@ -42915,19 +42995,22 @@
       <x:c r="B3" s="9" t="str">
         <x:v>第二章 信贷申请受理和贷前调查</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="n">
+      <x:c r="C3" s="9" t="str">
         <x:v>62494</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="n">
+      <x:c r="D3" s="29" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E3" s="9" t="n">
+      <x:c r="E3" s="29" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F3" s="9" t="n">
+      <x:c r="F3" s="29" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G3" s="29" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="n">
+      <x:c r="H3" s="30" t="n">
         <x:v>32</x:v>
       </x:c>
     </x:row>
@@ -42938,19 +43021,22 @@
       <x:c r="B4" s="9" t="str">
         <x:v>第三章 借款需求分析</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="n">
+      <x:c r="C4" s="9" t="str">
         <x:v>62495</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="n">
+      <x:c r="D4" s="29" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E4" s="9" t="n">
+      <x:c r="E4" s="29" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F4" s="9" t="n">
+      <x:c r="F4" s="29" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G4" s="29" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="n">
+      <x:c r="H4" s="30" t="n">
         <x:v>29</x:v>
       </x:c>
     </x:row>
@@ -42961,19 +43047,22 @@
       <x:c r="B5" s="9" t="str">
         <x:v>第四章 贷款环境风险分析</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="n">
+      <x:c r="C5" s="9" t="str">
         <x:v>62496</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="n">
+      <x:c r="D5" s="29" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E5" s="9" t="n">
+      <x:c r="E5" s="29" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F5" s="9" t="n">
+      <x:c r="F5" s="29" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G5" s="29" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="n">
+      <x:c r="H5" s="30" t="n">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -42984,19 +43073,22 @@
       <x:c r="B6" s="9" t="str">
         <x:v>第五章 客户分析与信用评级</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="n">
+      <x:c r="C6" s="9" t="str">
         <x:v>62497</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="n">
+      <x:c r="D6" s="29" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E6" s="9" t="n">
+      <x:c r="E6" s="29" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="F6" s="9" t="n">
+      <x:c r="F6" s="29" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G6" s="29" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="n">
+      <x:c r="H6" s="30" t="n">
         <x:v>44</x:v>
       </x:c>
     </x:row>
@@ -43007,19 +43099,22 @@
       <x:c r="B7" s="9" t="str">
         <x:v>第六章 固定资产贷款项目评估（初级不考此章节）</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="n">
+      <x:c r="C7" s="9" t="str">
         <x:v>62501</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="n">
+      <x:c r="D7" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="9" t="n">
+      <x:c r="E7" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="9" t="n">
+      <x:c r="F7" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="n">
+      <x:c r="G7" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="30" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -43030,19 +43125,22 @@
       <x:c r="B8" s="9" t="str">
         <x:v>第七章 担保管理</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="n">
+      <x:c r="C8" s="9" t="str">
         <x:v>62499</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="n">
+      <x:c r="D8" s="29" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="n">
+      <x:c r="E8" s="29" t="n">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="n">
+      <x:c r="F8" s="29" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="n">
+      <x:c r="H8" s="30" t="n">
         <x:v>48</x:v>
       </x:c>
     </x:row>
@@ -43053,19 +43151,22 @@
       <x:c r="B9" s="9" t="str">
         <x:v>第八章 信贷审批</x:v>
       </x:c>
-      <x:c r="C9" s="9" t="n">
+      <x:c r="C9" s="9" t="str">
         <x:v>62500</x:v>
       </x:c>
-      <x:c r="D9" s="9" t="n">
+      <x:c r="D9" s="29" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E9" s="9" t="n">
+      <x:c r="E9" s="29" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="n">
+      <x:c r="F9" s="29" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="n">
+      <x:c r="H9" s="30" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -43076,19 +43177,22 @@
       <x:c r="B10" s="9" t="str">
         <x:v>第九章 贷款合同与发放支付</x:v>
       </x:c>
-      <x:c r="C10" s="9" t="n">
+      <x:c r="C10" s="9" t="str">
         <x:v>62502</x:v>
       </x:c>
-      <x:c r="D10" s="9" t="n">
+      <x:c r="D10" s="29" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E10" s="9" t="n">
+      <x:c r="E10" s="29" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F10" s="9" t="n">
+      <x:c r="F10" s="29" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="n">
+      <x:c r="H10" s="30" t="n">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -43099,19 +43203,22 @@
       <x:c r="B11" s="9" t="str">
         <x:v>第十章 贷后管理</x:v>
       </x:c>
-      <x:c r="C11" s="9" t="n">
+      <x:c r="C11" s="9" t="str">
         <x:v>62503</x:v>
       </x:c>
-      <x:c r="D11" s="9" t="n">
+      <x:c r="D11" s="29" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E11" s="9" t="n">
+      <x:c r="E11" s="29" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F11" s="9" t="n">
+      <x:c r="F11" s="29" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G11" s="10" t="n">
+      <x:c r="H11" s="30" t="n">
         <x:v>31</x:v>
       </x:c>
     </x:row>
@@ -43122,19 +43229,22 @@
       <x:c r="B12" s="9" t="str">
         <x:v>第十一章 贷款风险分类 与贷款损失准备金的计提</x:v>
       </x:c>
-      <x:c r="C12" s="9" t="n">
+      <x:c r="C12" s="9" t="str">
         <x:v>62504</x:v>
       </x:c>
-      <x:c r="D12" s="9" t="n">
+      <x:c r="D12" s="29" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="9" t="n">
+      <x:c r="E12" s="29" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F12" s="9" t="n">
+      <x:c r="F12" s="29" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G12" s="10" t="n">
+      <x:c r="H12" s="30" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -43145,19 +43255,22 @@
       <x:c r="B13" s="9" t="str">
         <x:v>第十二章 不良贷款管理</x:v>
       </x:c>
-      <x:c r="C13" s="9" t="n">
+      <x:c r="C13" s="9" t="str">
         <x:v>62505</x:v>
       </x:c>
-      <x:c r="D13" s="9" t="n">
+      <x:c r="D13" s="29" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="E13" s="9" t="n">
+      <x:c r="E13" s="29" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F13" s="9" t="n">
+      <x:c r="F13" s="29" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G13" s="10" t="n">
+      <x:c r="H13" s="30" t="n">
         <x:v>29</x:v>
       </x:c>
     </x:row>
@@ -43168,38 +43281,44 @@
       <x:c r="B14" s="9" t="str">
         <x:v>附录</x:v>
       </x:c>
-      <x:c r="C14" s="9" t="n">
+      <x:c r="C14" s="9" t="str">
         <x:v>62616</x:v>
       </x:c>
-      <x:c r="D14" s="9" t="n">
+      <x:c r="D14" s="29" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E14" s="9" t="n">
+      <x:c r="E14" s="29" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F14" s="9" t="n">
+      <x:c r="F14" s="29" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G14" s="29" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G14" s="10" t="n">
+      <x:c r="H14" s="30" t="n">
         <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11" t="str"/>
-      <x:c r="B15" s="12" t="str">
+      <x:c r="A15" s="37" t="str"/>
+      <x:c r="B15" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="str"/>
-      <x:c r="D15" s="12" t="n">
+      <x:c r="C15" s="38" t="str"/>
+      <x:c r="D15" s="39" t="n">
         <x:v>687</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="n">
+      <x:c r="E15" s="39" t="n">
         <x:v>687</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="n">
+      <x:c r="F15" s="39" t="n">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="G15" s="39" t="n">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="n">
+      <x:c r="H15" s="39" t="n">
         <x:v>345</x:v>
       </x:c>
     </x:row>
@@ -43224,52 +43343,60 @@
         <x:v>内容</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="8" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="40" t="str">
         <x:v>科目</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>银行从业初级公司信贷</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="40" t="str">
         <x:v>范围</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>章节练习全量</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="40" t="str">
         <x:v>题目数量</x:v>
       </x:c>
       <x:c r="B4" s="10" t="n">
         <x:v>687</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="40" t="str">
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-08T22:32:59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+        <x:v>2026-09-10 00:15:56+08:00（本地时间）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="40" t="str">
         <x:v>来源链接</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>https://wx.233.com/center/study/tiku/chapter?domain=ccbp&amp;subjectId=752&amp;chapterType=1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="40" t="str">
+        <x:v>题量告警</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>无</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
+      <x:c r="A8" s="33" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="str">
-        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。</x:v>
+      <x:c r="B8" s="13" t="str">
+        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。 复用可信 Excel 中 1 道解析图片的既有文字；仅在来源题目 ID、题干、选项和答案均一致时复用。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R43379f981a264760"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R757e56d2300a42f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R86b55d21c0164c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rab03d7f2ecaf484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R9a49e783d5ab4cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R98feffd094b743d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43372,7 +43372,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 00:15:56+08:00（本地时间）</x:v>
+        <x:v>2026-09-10 15:08:20+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">

--- a/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级公司信贷_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rab03d7f2ecaf484f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R9a49e783d5ab4cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R98feffd094b743d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Ra8890f880ed244ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R2cce1379e9104081"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R934572c9f4c74dfa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43372,7 +43372,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 15:08:20+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 01:02:51+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
